--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>194932</t>
+          <t>73201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>92439</t>
+          <t>71019</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LAINIE MARYELL</t>
+          <t>JORGE ANTONIO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VILLASANA</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>VENEGAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,28 +887,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6463448080</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6461375003</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>INSURGENTE 505</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28-07-2001</t>
+          <t>16-02-1988</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LAINIEVILLASANA@GMAIL.COM</t>
+          <t>UA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>04-09-2023 19:54:28</t>
+          <t>15-02-2022 19:19:49</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -918,36 +922,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-02-2026 12:58:23</t>
+          <t>17-02-2026 20:02:17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>17-02-2026 20:01:45</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,14 +967,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26080521991200001802</t>
+          <t>26080522445770002827</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -979,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>269580</t>
+          <t>95110</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>67083</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MARIA TERESA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,12 +1026,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6461281787</t>
+          <t>6461986771</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PROLONGACION SAN LUIS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1029,60 +1041,56 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>08-11-1972</t>
+          <t>22-12-2001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TEREFLORESD@HOTMAIL.COM</t>
+          <t>MIGULRIOS35@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16-12-2024 16:41:32</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>25-05-2022 17:57:13</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>04-02-2026 08:17:44</t>
+          <t>16-02-2026 17:23:42</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>04-02-2026 08:17:04</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,18 +1098,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26080522069280002003</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522399060002737</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1118,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>73201</t>
+          <t>194932</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>71019</t>
+          <t>92439</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO</t>
+          <t>LAINIE MARYELL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MORAN</t>
+          <t>VILLASANA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VENEGAS</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,32 +1157,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6461375003</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>INSURGENTE 505</t>
-        </is>
-      </c>
+          <t>6463448080</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>16-02-1988</t>
+          <t>28-07-2001</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>UA@GMAIL.COM</t>
+          <t>LAINIEVILLASANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15-02-2022 19:19:49</t>
+          <t>04-09-2023 19:54:28</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1188,44 +1188,36 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-02-2026 20:02:17</t>
+          <t>01-02-2026 12:58:23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:01:45</t>
-        </is>
-      </c>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1233,14 +1225,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26080522445770002827</t>
+          <t>26080521991200001802</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1257,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>95110</t>
+          <t>269580</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92869</t>
+          <t>67083</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>MARIA TERESA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,12 +1284,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6461986771</t>
+          <t>6461281787</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>PROLONGACION SAN LUIS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,56 +1299,60 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22-12-2001</t>
+          <t>08-11-1972</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MIGULRIOS35@GMAIL.COM</t>
+          <t>TEREFLORESD@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>25-05-2022 17:57:13</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>16-12-2024 16:41:32</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>16-02-2026 17:23:42</t>
+          <t>04-02-2026 08:17:44</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>04-02-2026 08:17:04</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1364,14 +1360,18 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26080522399060002737</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26080522069280002003</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2893,12 +2893,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340199</t>
+          <t>341021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2908,17 +2908,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t xml:space="preserve">VICTORIA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>TOLEDO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2928,28 +2928,28 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6463458118</t>
+          <t>6623276252</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>04-03-2006</t>
+          <t>29-08-2006</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>VEGAPELAYO1@GMAIL.COM</t>
+          <t>SANDOVAL1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 15:04:45</t>
+          <t>04-02-2026 14:49:52</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2974,18 +2974,18 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 15:06:10</t>
+          <t>04-02-2026 14:52:30</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26080522013810001858</t>
+          <t>26080522076440002031</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3008,24 +3008,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341021</t>
+          <t>340199</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA </t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TOLEDO</t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6623276252</t>
+          <t>6463458118</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>29-08-2006</t>
+          <t>04-03-2006</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SANDOVAL1@GMAIL.COM</t>
+          <t>VEGAPELAYO1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-02-2026 14:49:52</t>
+          <t>02-02-2026 15:04:45</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3101,18 +3101,18 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-02-2026 14:52:30</t>
+          <t>02-02-2026 15:06:10</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26080522076440002031</t>
+          <t>26080522013810001858</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3135,24 +3135,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340485</t>
+          <t>340356</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18303</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t xml:space="preserve">PAULINA LIZETH </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CHEGUEZ</t>
+          <t xml:space="preserve"> MERCADO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6462879836</t>
+          <t>6243206497</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3193,17 +3193,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20-05-2005</t>
+          <t>22-06-2006</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ANDREA.CHEGUEZ2005@GMAIL.COM</t>
+          <t>PAULINACESEÑA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-02-2026 09:07:18</t>
+          <t>02-02-2026 18:54:50</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3228,18 +3228,18 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-02-2026 09:57:15</t>
+          <t>02-02-2026 18:56:21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26080522071110002012</t>
+          <t>26080522021340001884</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3262,24 +3262,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340356</t>
+          <t>340388</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18206</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3289,17 +3289,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULINA LIZETH </t>
+          <t xml:space="preserve">VICTOR GERARDO </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CESEÑA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MERCADO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3309,53 +3309,53 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6243206497</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6462866658</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22-06-2006</t>
+          <t>28-05-1998</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PAULINACESEÑA1@GMAIL.COM</t>
+          <t>VICTORCOTA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-02-2026 18:54:50</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 20:29:45</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-02-2026 18:56:21</t>
+          <t>02-02-2026 20:54:24</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3363,13 +3363,21 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>02-02-2026 20:45:22</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3377,14 +3385,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26080522021340001884</t>
+          <t>26080522023450001894</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3401,12 +3409,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340388</t>
+          <t>340485</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3416,17 +3424,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR GERARDO </t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CHEGUEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3436,75 +3444,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6462866658</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462879836</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-05-1998</t>
+          <t>20-05-2005</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>VICTORCOTA1@GMAIL.COM</t>
+          <t>ANDREA.CHEGUEZ2005@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-02-2026 20:29:45</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>03-02-2026 09:07:18</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-02-2026 20:54:24</t>
+          <t>04-02-2026 09:57:15</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>02-02-2026 20:45:22</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3512,36 +3512,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26080522023450001894</t>
+          <t>26080522071110002012</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340651</t>
+          <t>341816</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">JACARANDA </t>
+          <t>PEDRO RAMON</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6461932530</t>
+          <t>6461517060</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3581,29 +3581,25 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>01-06-1979</t>
+          <t>31-08-1981</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>GONZAHERNANDEZ1@GMAIL.COM</t>
+          <t>PEDROARANDA12@GMIAL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-02-2026 16:08:16</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 11:46:11</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3611,27 +3607,27 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-02-2026 16:23:35</t>
+          <t>07-02-2026 11:56:52</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>03-02-2026 16:22:17</t>
+          <t>07-02-2026 11:56:02</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3641,7 +3637,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3651,19 +3647,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26080522045290001944</t>
+          <t>26080522160400002214</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Aaron Felipe Aguilar Grave</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3675,12 +3671,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340812</t>
+          <t>340651</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3690,17 +3686,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t xml:space="preserve">JACARANDA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CARDOSO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3710,7 +3706,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6461504499</t>
+          <t>6461932530</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3720,22 +3716,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30-08-1993</t>
+          <t>01-06-1979</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RUBENCARDOSO@GMAIL.COM</t>
+          <t>GONZAHERNANDEZ1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-02-2026 19:20:39</t>
+          <t>03-02-2026 16:08:16</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3745,22 +3741,22 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-02-2026 19:27:16</t>
+          <t>03-02-2026 16:23:35</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3770,7 +3766,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>03-02-2026 19:26:45</t>
+          <t>03-02-2026 16:22:17</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3790,36 +3786,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26080522056050001974</t>
+          <t>26080522045290001944</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>337214</t>
+          <t>340812</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3829,17 +3825,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LILIANA </t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AMPARANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>CARDOSO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3849,7 +3845,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6462108123</t>
+          <t>6461504499</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3859,53 +3855,57 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30-03-1975</t>
+          <t>30-08-1993</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ARAMIREZ771@TGMAIL.COM</t>
+          <t>RUBENCARDOSO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>23-01-2026 11:15:39</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>03-02-2026 19:20:39</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>06-02-2026 10:45:48</t>
+          <t>03-02-2026 19:27:16</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>06-02-2026 10:44:57</t>
+          <t>03-02-2026 19:26:45</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3925,36 +3925,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26080522133760002160</t>
+          <t>26080522056050001974</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341836</t>
+          <t>342141</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3964,17 +3964,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIREYA DEL ROSARIO </t>
+          <t xml:space="preserve">BRUNO </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLLANTES </t>
+          <t xml:space="preserve">VELASCO </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3984,28 +3984,28 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6461505249</t>
+          <t>6461854488</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>25-09-1958</t>
+          <t>30-12-1993</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>COLLANTES1@GMAIL.COM</t>
+          <t>BRUNOVELASCORODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>07-02-2026 13:55:26</t>
+          <t>09-02-2026 12:44:20</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>07-02-2026 13:57:17</t>
+          <t>09-02-2026 12:45:41</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -4052,14 +4052,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26080522161990002219</t>
+          <t>26080522190770002280</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4076,12 +4076,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341692</t>
+          <t>341836</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JAIME ULISES</t>
+          <t xml:space="preserve">MIREYA DEL ROSARIO </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEON </t>
+          <t xml:space="preserve">COLLANTES </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4111,75 +4111,67 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6463868081</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461505249</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23-05-2002</t>
+          <t>25-09-1958</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>LEONCHAPARRO1@GMAIL.COM</t>
+          <t>COLLANTES1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>06-02-2026 19:48:31</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>07-02-2026 13:55:26</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>06-02-2026 19:53:01</t>
+          <t>07-02-2026 13:57:17</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>06-02-2026 19:52:22</t>
-        </is>
-      </c>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4187,19 +4179,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26080522147500002197</t>
+          <t>26080522161990002219</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4211,12 +4203,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341816</t>
+          <t>341692</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4226,17 +4218,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEDRO RAMON</t>
+          <t>JAIME ULISES</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t xml:space="preserve">LEON </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4246,7 +4238,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6461517060</t>
+          <t>6463868081</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4261,17 +4253,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31-08-1981</t>
+          <t>23-05-2002</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PEDROARANDA12@GMIAL.COM</t>
+          <t>LEONCHAPARRO1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>07-02-2026 11:46:11</t>
+          <t>06-02-2026 19:48:31</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4292,17 +4284,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>07-02-2026 11:56:52</t>
+          <t>06-02-2026 19:53:01</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>07-02-2026 11:56:02</t>
+          <t>06-02-2026 19:52:22</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4322,7 +4314,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26080522160400002214</t>
+          <t>26080522147500002197</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4334,7 +4326,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4346,12 +4338,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342189</t>
+          <t>337214</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4361,17 +4353,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">HENRY JOSE </t>
+          <t xml:space="preserve">LILIANA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>AMPARANO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4381,67 +4373,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6461439409</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6462108123</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10-03-1985</t>
+          <t>30-03-1975</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CHAVEZMORALES1@GMAIL.COM</t>
+          <t>ARAMIREZ771@TGMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:49</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>23-01-2026 11:15:39</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 14:46:17</t>
+          <t>06-02-2026 10:45:48</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>06-02-2026 10:44:57</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4449,19 +4449,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26080522193810002291</t>
+          <t>26080522133760002160</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4608,12 +4608,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342141</t>
+          <t>342568</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO </t>
+          <t xml:space="preserve">VIVIANA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELASCO </t>
+          <t xml:space="preserve">SALINAS </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4643,67 +4643,75 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6461854488</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6461035830</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUENTE </t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30-12-1993</t>
+          <t>29-12-1997</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BRUNOVELASCORODRIGUEZ@GMAIL.COM</t>
+          <t>ZEPEDAV080@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 12:44:20</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 09:34:54</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 12:45:41</t>
+          <t>10-02-2026 09:45:15</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>10-02-2026 09:43:52</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4711,19 +4719,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26080522190770002280</t>
+          <t>26080522227420002380</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4735,12 +4743,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342259</t>
+          <t>342189</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4750,17 +4758,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t xml:space="preserve">HENRY JOSE </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAUTISTA </t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4770,32 +4778,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6461486212</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461439409</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17-02-1985</t>
+          <t>10-03-1985</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BAUTISTAGONZALEZ1@GMAIL.COM</t>
+          <t>CHAVEZMORALES1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 16:33:32</t>
+          <t>09-02-2026 14:44:49</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4805,44 +4809,36 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>09-02-2026 16:38:00</t>
+          <t>09-02-2026 14:46:17</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>09-02-2026 16:37:17</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4850,14 +4846,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26080522198950002301</t>
+          <t>26080522193810002291</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4874,12 +4870,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>340220</t>
+          <t>342259</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4889,17 +4885,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DIEGO ALEJANDRO</t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>REVELES</t>
+          <t xml:space="preserve">BAUTISTA </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4909,28 +4905,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6642963182</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6461486212</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17-02-2000</t>
+          <t>17-02-1985</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DIEGOTORRRES1@GMAIL.COM</t>
+          <t>BAUTISTAGONZALEZ1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-02-2026 15:33:20</t>
+          <t>09-02-2026 16:33:32</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4940,36 +4940,44 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-02-2026 15:34:36</t>
+          <t>09-02-2026 16:38:00</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>09-02-2026 16:37:17</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4977,19 +4985,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26080522014760001867</t>
+          <t>26080522198950002301</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5001,12 +5009,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342075</t>
+          <t>342746</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5016,17 +5024,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>JESUS DANIEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GARFIAS</t>
+          <t>FONSECA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5036,7 +5044,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6462739845</t>
+          <t>6627358017</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5047,17 +5055,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>09-02-2004</t>
+          <t>03-10-2000</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CRALOS.GARFIAS@UABC.EDU.MX</t>
+          <t>FONSECAJESUS25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 09:39:43</t>
+          <t>10-02-2026 17:19:18</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5082,12 +5090,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 09:41:39</t>
+          <t>10-02-2026 17:20:37</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -5104,7 +5112,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26080522186670002267</t>
+          <t>26080522239370002419</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5116,7 +5124,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5128,12 +5136,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340546</t>
+          <t>342712</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>20529</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5143,17 +5151,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMA KARINA </t>
+          <t xml:space="preserve">MIA VALERIA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5163,12 +5171,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6462760004</t>
+          <t>6161246640</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AVENIDA DE LAS AMÉRICAS 796</t>
+          <t>DEL ROBLE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5178,20 +5186,24 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>03-04-1997</t>
+          <t>02-01-2005</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ALMAH2778@GMAIL.CON</t>
+          <t>MIAGUERRA54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>03-02-2026 12:27:28</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>10-02-2026 16:32:54</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5209,27 +5221,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>03-02-2026 12:27:29</t>
+          <t>23-02-2026 18:56:39</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>03-02-2026 12:27:29</t>
+          <t>23-02-2026 18:56:01</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5239,10 +5251,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26080522038410001925</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+          <t>26080522597810003114</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5263,12 +5279,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>340591</t>
+          <t>339888</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5278,17 +5294,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRIAM LINETH </t>
+          <t xml:space="preserve">CAROLINA </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5298,10 +5314,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3111583964</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6461281526</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5309,17 +5329,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>04-10-1999</t>
+          <t>19-09-1997</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ROMEROOCHOA1@GMAIL.COM</t>
+          <t>MUSIKARO8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>03-02-2026 14:18:11</t>
+          <t>02-02-2026 07:54:47</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5329,36 +5349,44 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>03-02-2026 14:19:50</t>
+          <t>02-02-2026 08:00:19</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>02-02-2026 07:58:28</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5366,36 +5394,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26080522040970001933</t>
+          <t>26080522000340001820</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>339888</t>
+          <t>342075</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5405,17 +5433,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAROLINA </t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>GARFIAS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5425,32 +5453,28 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6461281526</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462739845</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19-09-1997</t>
+          <t>09-02-2004</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MUSIKARO8@GMAIL.COM</t>
+          <t>CRALOS.GARFIAS@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>02-02-2026 07:54:47</t>
+          <t>09-02-2026 09:39:43</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5460,12 +5484,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5475,29 +5499,21 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>02-02-2026 08:00:19</t>
+          <t>09-02-2026 09:41:39</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>02-02-2026 07:58:28</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5505,7 +5521,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26080522000340001820</t>
+          <t>26080522186670002267</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5517,7 +5533,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5529,12 +5545,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342456</t>
+          <t>343520</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>21337</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5544,17 +5560,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL GERMAN </t>
+          <t>IRISS ANNELIS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t xml:space="preserve"> OCHOA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5564,28 +5580,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6461289040</t>
+          <t>6648515854</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>02-01-1998</t>
+          <t>22-05-2007</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MRAMOST98@HOTMAIL.COM</t>
+          <t>RAMIREZIRISS23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>09-02-2026 19:48:26</t>
+          <t>13-02-2026 15:45:04</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5610,18 +5626,18 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>09-02-2026 19:50:37</t>
+          <t>13-02-2026 15:47:14</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5632,7 +5648,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26080522212170002344</t>
+          <t>26080522323130002622</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5656,12 +5672,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342568</t>
+          <t>342456</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5671,17 +5687,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIVIANA </t>
+          <t xml:space="preserve">MIGUEL GERMAN </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALINAS </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5691,75 +5707,67 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6461035830</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUENTE </t>
-        </is>
-      </c>
+          <t>6461289040</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>29-12-1997</t>
+          <t>02-01-1998</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ZEPEDAV080@GMAIL.COM</t>
+          <t>MRAMOST98@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10-02-2026 09:34:54</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>09-02-2026 19:48:26</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10-02-2026 09:45:15</t>
+          <t>09-02-2026 19:50:37</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>10-02-2026 09:43:52</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5767,19 +5775,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26080522227420002380</t>
+          <t>26080522212170002344</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5934,12 +5942,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340829</t>
+          <t>340220</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5949,17 +5957,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JOVANA</t>
+          <t>DIEGO ALEJANDRO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LARIOS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>REVELES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5969,28 +5977,28 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6461276781</t>
+          <t>6642963182</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>24-07-1989</t>
+          <t>17-02-2000</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>JOVANALARIOS13@GMAIL.COM</t>
+          <t>DIEGOTORRRES1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-02-2026 20:04:47</t>
+          <t>02-02-2026 15:33:20</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6015,18 +6023,18 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-02-2026 20:06:10</t>
+          <t>02-02-2026 15:34:36</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -6037,7 +6045,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26080522057330001981</t>
+          <t>26080522014760001867</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6049,7 +6057,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6061,12 +6069,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>340918</t>
+          <t>341096</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6076,17 +6084,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MARIANA ELIDE</t>
+          <t>ADAN ALEJANDRO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t xml:space="preserve">ROBLES </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLACENCIA </t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6096,53 +6104,53 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6462372600</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6461017657</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>12-08-2002</t>
+          <t>30-09-1990</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>MAELGUZ1997@GMAIL.COM</t>
+          <t>ADANROBLES1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>04-02-2026 09:40:41</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 17:07:45</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>04-02-2026 09:42:07</t>
+          <t>04-02-2026 17:13:37</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6150,13 +6158,21 @@
           <t>04-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>04-02-2026 17:13:04</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6164,14 +6180,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26080522070810002008</t>
+          <t>26080522081730002044</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6188,12 +6204,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>340965</t>
+          <t>343298</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6203,17 +6219,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROBERTO </t>
+          <t>RODOLFO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ARIPEZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>BURGOIN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6223,7 +6239,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6461514504</t>
+          <t>6461015893</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6234,17 +6250,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>07-06-1962</t>
+          <t>02-03-1963</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>RHG6206@HOTMAIL.COM</t>
+          <t>RODOLFOBURGOIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>04-02-2026 12:21:43</t>
+          <t>12-02-2026 15:59:32</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6259,22 +6275,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>04-02-2026 12:23:09</t>
+          <t>12-02-2026 16:00:52</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -6291,36 +6307,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26080522073340002018</t>
+          <t>26080522296690002550</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>340969</t>
+          <t>340396</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6330,17 +6346,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t xml:space="preserve">ARGENIS ISRAEL </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GLAVEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6350,7 +6366,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6562453111</t>
+          <t>6462867842</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6361,17 +6377,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17-09-1994</t>
+          <t>12-05-2005</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>VGALVEZVARGAS@GMAIL.COM</t>
+          <t>GONZALEZARGENIS1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>04-02-2026 12:28:52</t>
+          <t>02-02-2026 20:56:58</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6396,18 +6412,18 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>04-02-2026 12:29:56</t>
+          <t>02-02-2026 20:59:14</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -6418,7 +6434,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26080522073480002020</t>
+          <t>26080522023520001895</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6430,24 +6446,24 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342746</t>
+          <t>340546</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6457,17 +6473,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JESUS DANIEL</t>
+          <t xml:space="preserve">ALMA KARINA </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FONSECA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6477,67 +6493,75 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6627358017</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6462760004</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>AVENIDA DE LAS AMÉRICAS 796</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>03-10-2000</t>
+          <t>03-04-1997</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>FONSECAJESUS25@GMAIL.COM</t>
+          <t>ALMAH2778@GMAIL.CON</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 17:19:18</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 12:27:28</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 17:20:37</t>
+          <t>03-02-2026 12:27:29</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>03-02-2026 12:27:29</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6545,36 +6569,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26080522239370002419</t>
+          <t>26080522038410001925</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343298</t>
+          <t>340591</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6584,17 +6608,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RODOLFO</t>
+          <t xml:space="preserve">MIRIAM LINETH </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ARIPEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BURGOIN</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6604,28 +6628,28 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6461015893</t>
+          <t>3111583964</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>02-03-1963</t>
+          <t>04-10-1999</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>RODOLFOBURGOIN@GMAIL.COM</t>
+          <t>ROMEROOCHOA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>12-02-2026 15:59:32</t>
+          <t>03-02-2026 14:18:11</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6650,12 +6674,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>12-02-2026 16:00:52</t>
+          <t>03-02-2026 14:19:50</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -6672,7 +6696,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26080522296690002550</t>
+          <t>26080522040970001933</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6684,12 +6708,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -6823,12 +6847,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342723</t>
+          <t>343185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6838,17 +6862,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RAFAEL LEONARDO</t>
+          <t>FERNANDA CELIA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">ARAUJO </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6858,39 +6882,35 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6421374093</t>
+          <t>6463842082</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BAHIA MAGADALENA 313</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>20-11-2010</t>
+          <t>10-04-2002</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>LEONARDOGUERRA12@GMAIL.COM</t>
+          <t>FERNADNACELIAARAUJOLOPEZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>10-02-2026 16:50:19</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 08:40:25</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6908,17 +6928,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>18-02-2026 18:12:04</t>
+          <t>12-02-2026 08:45:43</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>18-02-2026 18:11:28</t>
+          <t>12-02-2026 08:45:03</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6938,14 +6958,10 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26080522471680002882</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522289620002530</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6954,24 +6970,24 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>340396</t>
+          <t>343351</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6981,17 +6997,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGENIS ISRAEL </t>
+          <t>JOSE MARIA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GARFIAS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7001,7 +7017,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6462867842</t>
+          <t>6462677544</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7012,17 +7028,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>12-05-2005</t>
+          <t>04-05-2009</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>GONZALEZARGENIS1@GMAIL.COM</t>
+          <t>GARFIASSILVA.JOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:58</t>
+          <t>12-02-2026 17:52:23</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7047,12 +7063,12 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>02-02-2026 20:59:14</t>
+          <t>12-02-2026 17:53:22</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -7069,7 +7085,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26080522023520001895</t>
+          <t>26080522300960002562</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7081,7 +7097,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7093,12 +7109,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343520</t>
+          <t>343448</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21337</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7108,19 +7124,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IRISS ANNELIS</t>
+          <t>NELLY</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>RAMIREZ</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OCHOA</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>52</t>
@@ -7128,10 +7144,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6648515854</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6461980165</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>LAZARO CARDENAS</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7139,42 +7159,38 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22-05-2007</t>
+          <t>08-12-1978</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>RAMIREZIRISS23@GMAIL.COM</t>
+          <t>NELLYRAMIREZ25@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>13-02-2026 15:45:04</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 09:32:16</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>13-02-2026 15:47:14</t>
+          <t>13-02-2026 09:38:42</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7182,13 +7198,21 @@
           <t>13-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>13-02-2026 09:37:53</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7196,19 +7220,19 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26080522323130002622</t>
+          <t>26080522317600002604</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7220,12 +7244,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>341096</t>
+          <t>340829</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7235,17 +7259,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ADAN ALEJANDRO</t>
+          <t>JOVANA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROBLES </t>
+          <t>LARIOS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7255,75 +7279,67 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6461017657</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461276781</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30-09-1990</t>
+          <t>24-07-1989</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ADANROBLES1@GMAIL.COM</t>
+          <t>JOVANALARIOS13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>04-02-2026 17:07:45</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>03-02-2026 20:04:47</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>04-02-2026 17:13:37</t>
+          <t>03-02-2026 20:06:10</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>04-02-2026 17:13:04</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7331,19 +7347,19 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26080522081730002044</t>
+          <t>26080522057330001981</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Aaron Felipe Aguilar Grave</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7355,12 +7371,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343185</t>
+          <t>340918</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7370,17 +7386,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FERNANDA CELIA</t>
+          <t>MARIANA ELIDE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARAUJO </t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">PLACENCIA </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7390,14 +7406,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6463842082</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>BAHIA MAGADALENA 313</t>
-        </is>
-      </c>
+          <t>6462372600</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7405,60 +7417,56 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>10-04-2002</t>
+          <t>12-08-2002</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>FERNADNACELIAARAUJOLOPEZ@HOTMAIL.COM</t>
+          <t>MAELGUZ1997@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>12-02-2026 08:40:25</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>04-02-2026 09:40:41</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>12-02-2026 08:45:43</t>
+          <t>04-02-2026 09:42:07</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>12-02-2026 08:45:03</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7466,19 +7474,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26080522289620002530</t>
+          <t>26080522070810002008</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7490,12 +7498,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343351</t>
+          <t>340965</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7505,17 +7513,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JOSE MARIA</t>
+          <t xml:space="preserve">ROBERTO </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GARFIAS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7525,7 +7533,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6462677544</t>
+          <t>6461514504</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7536,17 +7544,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>04-05-2009</t>
+          <t>07-06-1962</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>GARFIASSILVA.JOSE@GMAIL.COM</t>
+          <t>RHG6206@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>12-02-2026 17:52:23</t>
+          <t>04-02-2026 12:21:43</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7571,18 +7579,18 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>12-02-2026 17:53:22</t>
+          <t>04-02-2026 12:23:09</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V54" t="inlineStr"/>
@@ -7593,7 +7601,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26080522300960002562</t>
+          <t>26080522073340002018</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7605,24 +7613,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>343448</t>
+          <t>340969</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7632,17 +7640,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NELLY</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>GLAVEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7652,75 +7660,67 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6461980165</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>LAZARO CARDENAS</t>
-        </is>
-      </c>
+          <t>6562453111</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>08-12-1978</t>
+          <t>17-09-1994</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>NELLYRAMIREZ25@HOTMAIL.COM</t>
+          <t>VGALVEZVARGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>13-02-2026 09:32:16</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>04-02-2026 12:28:52</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>13-02-2026 09:38:42</t>
+          <t>04-02-2026 12:29:56</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>13-02-2026 09:37:53</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7728,36 +7728,36 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26080522317600002604</t>
+          <t>26080522073480002020</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>341153</t>
+          <t>342723</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7767,17 +7767,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA </t>
+          <t>RAFAEL LEONARDO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">RANGEL </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7787,67 +7787,79 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6461483552</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>6421374093</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>27-08-2007</t>
+          <t>20-11-2010</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>RANGELGUZMAN1@GMAIL.COM</t>
+          <t>LEONARDOGUERRA12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>04-02-2026 18:44:51</t>
+          <t>10-02-2026 16:50:19</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>04-02-2026 18:45:48</t>
+          <t>18-02-2026 18:12:04</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:11:28</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7855,14 +7867,18 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26080522086240002050</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
+          <t>26080522471680002882</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7879,12 +7895,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344305</t>
+          <t>344671</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7894,17 +7910,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>REINA KETZALLI</t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BANDA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESPINOZA</t>
+          <t xml:space="preserve"> BADILLO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7914,28 +7930,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6151551917</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6461191119</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>09-11-2007</t>
+          <t>13-07-1996</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>REINABANDA55@GMAIL.COM</t>
+          <t>ANTONIOVALBADILLO234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16-02-2026 18:39:30</t>
+          <t>17-02-2026 18:55:18</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -7945,36 +7965,44 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>16-02-2026 18:41:01</t>
+          <t>17-02-2026 19:00:16</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>17-02-2026 18:59:28</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7982,14 +8010,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26080522405320002747</t>
+          <t>26080522443150002818</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8121,24 +8149,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>341999</t>
+          <t>341153</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8148,17 +8176,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TANIA JASMIN</t>
+          <t xml:space="preserve">DANIA </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTRADA </t>
+          <t xml:space="preserve">RANGEL </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8168,14 +8196,10 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6461874843</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461483552</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8183,60 +8207,56 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>02-08-1984</t>
+          <t>27-08-2007</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>TANIAESTRADA797@GMAIL.COM</t>
+          <t>RANGELGUZMAN1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>09-02-2026 05:30:17</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>04-02-2026 18:44:51</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>09-02-2026 05:36:30</t>
+          <t>04-02-2026 18:45:48</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>09-02-2026 05:35:38</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8244,24 +8264,24 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26080522180640002238</t>
+          <t>26080522086240002050</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -8403,12 +8423,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>342338</t>
+          <t>344090</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8418,17 +8438,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DANIEL EDUARDO</t>
+          <t xml:space="preserve">XIMENA </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HUICAB</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8438,67 +8458,79 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9811592635</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>6461287472</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>23-02-1998</t>
+          <t>22-06-2006</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>DANIELHUICAB@GMAIL.COM</t>
+          <t>XIMENAHERNANDEZ566@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:39</t>
+          <t>16-02-2026 14:14:17</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>09-02-2026 17:36:58</t>
+          <t>17-02-2026 13:19:13</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>17-02-2026 13:17:34</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8506,14 +8538,22 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26080522203080002312</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+          <t>26080522427590002778</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8530,12 +8570,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344671</t>
+          <t>344305</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8545,17 +8585,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t>REINA KETZALLI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>BANDA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BADILLO</t>
+          <t xml:space="preserve"> ESPINOZA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8565,32 +8605,28 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6461191119</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6151551917</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>13-07-1996</t>
+          <t>09-11-2007</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ANTONIOVALBADILLO234@GMAIL.COM</t>
+          <t>REINABANDA55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>17-02-2026 18:55:18</t>
+          <t>16-02-2026 18:39:30</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8600,44 +8636,36 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>17-02-2026 19:00:16</t>
+          <t>16-02-2026 18:41:01</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>17-02-2026 18:59:28</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8645,14 +8673,14 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26080522443150002818</t>
+          <t>26080522405320002747</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8669,12 +8697,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344090</t>
+          <t>341999</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8684,17 +8712,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">XIMENA </t>
+          <t>TANIA JASMIN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">ESTRADA </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8704,7 +8732,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6461287472</t>
+          <t>6461874843</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8719,24 +8747,20 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>22-06-2006</t>
+          <t>02-08-1984</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>XIMENAHERNANDEZ566@GMAIL.COM</t>
+          <t>TANIAESTRADA797@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>16-02-2026 14:14:17</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 05:30:17</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8754,17 +8778,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>17-02-2026 13:19:13</t>
+          <t>09-02-2026 05:36:30</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>17-02-2026 13:17:34</t>
+          <t>09-02-2026 05:35:38</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8774,7 +8798,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8784,19 +8808,11 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26080522427590002778</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
-        </is>
-      </c>
+          <t>26080522180640002238</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
           <t>499</t>
@@ -8804,7 +8820,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8816,12 +8832,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344526</t>
+          <t>342133</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8831,17 +8847,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>JOSE CARLO</t>
+          <t>YASMIN CAROLINA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t xml:space="preserve">LARA </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8851,28 +8867,32 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6469478205</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6462272759</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>09-03-2009</t>
+          <t>08-02-1987</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>GALVANJC66@GMAIL.COM</t>
+          <t>YASMIN.CLR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>17-02-2026 15:22:33</t>
+          <t>09-02-2026 12:27:09</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8882,36 +8902,44 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>17-02-2026 15:23:39</t>
+          <t>09-02-2026 12:31:24</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>09-02-2026 12:30:44</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8919,36 +8947,36 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26080522431360002789</t>
+          <t>26080522190470002279</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>342133</t>
+          <t>344526</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8958,17 +8986,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>YASMIN CAROLINA</t>
+          <t>JOSE CARLO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LARA </t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8978,32 +9006,28 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6462272759</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6469478205</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>08-02-1987</t>
+          <t>09-03-2009</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>YASMIN.CLR@GMAIL.COM</t>
+          <t>GALVANJC66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>09-02-2026 12:27:09</t>
+          <t>17-02-2026 15:22:33</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9013,44 +9037,36 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>09-02-2026 12:31:24</t>
+          <t>17-02-2026 15:23:39</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>09-02-2026 12:30:44</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9058,24 +9074,24 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26080522190470002279</t>
+          <t>26080522431360002789</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9237,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>345392</t>
+          <t>344410</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>87557</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9236,17 +9252,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PAULINA ABRIL</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9256,10 +9272,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6461024876</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>6461298989</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9267,56 +9287,64 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>11-09-1996</t>
+          <t>24-05-1956</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>PAULINAABRIL45@GMAIL.COM</t>
+          <t>PADILLARAQUEL45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>20-02-2026 18:27:25</t>
+          <t>17-02-2026 08:14:06</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>20-02-2026 18:29:17</t>
+          <t>17-02-2026 08:18:21</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:17:21</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9324,36 +9352,36 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26080522534310003010</t>
+          <t>26080522421710002766</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344601</t>
+          <t>345392</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>87557</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9363,17 +9391,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIN DE JESUS </t>
+          <t>PAULINA ABRIL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t xml:space="preserve"> PAZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9383,33 +9411,33 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6462247390</t>
+          <t>6461024876</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>22-01-1992</t>
+          <t>11-09-1996</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>RAMIREZBRACO554@GMAIL.COM</t>
+          <t>PAULINAABRIL45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>17-02-2026 17:19:31</t>
+          <t>20-02-2026 18:27:25</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -9429,12 +9457,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>19-02-2026 17:18:11</t>
+          <t>20-02-2026 18:29:17</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -9451,19 +9479,11 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26080522500880002947</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
-        </is>
-      </c>
+          <t>26080522534310003010</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
           <t>549</t>
@@ -9483,12 +9503,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>344410</t>
+          <t>342338</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>20156</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9498,17 +9518,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>DANIEL EDUARDO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>HUICAB</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9518,79 +9538,67 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6461298989</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>9811592635</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>24-05-1956</t>
+          <t>23-02-1998</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>PADILLARAQUEL45@GMAIL.COM</t>
+          <t>DANIELHUICAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>17-02-2026 08:14:06</t>
+          <t>09-02-2026 17:35:39</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>17-02-2026 08:18:21</t>
+          <t>09-02-2026 17:36:58</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>17-02-2026 08:17:21</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9598,14 +9606,14 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26080522421710002766</t>
+          <t>26080522203080002312</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9761,12 +9769,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>342711</t>
+          <t>344601</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9776,17 +9784,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL LEONARDO </t>
+          <t xml:space="preserve">MARTIN DE JESUS </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>URBINA</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9796,14 +9804,10 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6161070933</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462247390</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9811,64 +9815,56 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>07-12-1978</t>
+          <t>22-01-1992</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>FELIXUBINA66@GMAIL.COM</t>
+          <t>RAMIREZBRACO554@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>10-02-2026 16:32:25</t>
+          <t>17-02-2026 17:19:31</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:47</t>
+          <t>19-02-2026 17:18:11</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:14:19</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9876,18 +9872,22 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26080522471840002883</t>
+          <t>26080522500880002947</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -10031,12 +10031,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>345108</t>
+          <t>344979</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10046,17 +10046,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MARTHA IMELDA</t>
+          <t>INNEL CAROLINA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DRAGUSTINOVIS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6461798580</t>
+          <t>6462234346</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -10081,17 +10081,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>10-04-1967</t>
+          <t>11-09-1985</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>DRAGUSTINOVISMARTHA145@GMAIL.COM</t>
+          <t>INNELYA_11@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>19-02-2026 15:42:21</t>
+          <t>19-02-2026 06:53:45</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10116,17 +10116,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>19-02-2026 15:50:59</t>
+          <t>23-02-2026 18:33:46</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>19-02-2026 15:50:24</t>
+          <t>23-02-2026 18:31:37</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -10146,11 +10146,19 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26080522497630002935</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
+          <t>26080522596180003109</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>NAOMI LIZETH FLORES SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>649</t>
@@ -10158,24 +10166,24 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>343142</t>
+          <t>345108</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>87273</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10185,17 +10193,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>MARTHA IMELDA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t>DRAGUSTINOVIS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AZPE</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10205,7 +10213,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6463062217</t>
+          <t>6461798580</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -10215,53 +10223,57 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>14-06-1995</t>
+          <t>10-04-1967</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ESPINOZADAVID25@GMAIL.COM</t>
+          <t>DRAGUSTINOVISMARTHA145@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>11-02-2026 21:15:20</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>19-02-2026 15:42:21</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>11-02-2026 21:19:31</t>
+          <t>19-02-2026 15:50:59</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>11-02-2026 21:19:04</t>
+          <t>19-02-2026 15:50:24</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10271,7 +10283,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10281,14 +10293,14 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26080522279400002518</t>
+          <t>26080522497630002935</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -10305,12 +10317,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>342722</t>
+          <t>343812</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10320,12 +10332,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BERENICE</t>
+          <t xml:space="preserve">ENRIQUE CESAR </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -10340,7 +10352,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6469475604</t>
+          <t>6461505634</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -10350,29 +10362,25 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>24-02-1978</t>
+          <t>15-06-1973</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>GUERRABERENICE34@MIAL.COM</t>
+          <t>SANCHEZGARCIAS65@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>10-02-2026 16:49:08</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 11:24:34</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10390,17 +10398,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>18-02-2026 18:06:32</t>
+          <t>15-02-2026 11:27:07</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>18-02-2026 18:05:46</t>
+          <t>15-02-2026 11:26:42</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10420,14 +10428,10 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26080522471390002879</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522364410002661</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
@@ -10448,12 +10452,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>343812</t>
+          <t>342711</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10463,17 +10467,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUE CESAR </t>
+          <t xml:space="preserve">RAFAEL LEONARDO </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>URBINA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10483,7 +10487,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6461505634</t>
+          <t>6161070933</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -10498,20 +10502,24 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>15-06-1973</t>
+          <t>07-12-1978</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>SANCHEZGARCIAS65@GMAIL.COM</t>
+          <t>FELIXUBINA66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>15-02-2026 11:24:34</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>10-02-2026 16:32:25</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10529,17 +10537,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>15-02-2026 11:27:07</t>
+          <t>18-02-2026 18:14:47</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>15-02-2026 11:26:42</t>
+          <t>18-02-2026 18:14:19</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10559,10 +10567,14 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26080522364410002661</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr"/>
+          <t>26080522471840002883</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
@@ -10583,12 +10595,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>343052</t>
+          <t>342722</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20869</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10598,17 +10610,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBI ESMERALDA </t>
+          <t>BERENICE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTEZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10618,7 +10630,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6461323517</t>
+          <t>6469475604</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -10633,22 +10645,22 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>07-02-1994</t>
+          <t>24-02-1978</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>PONCEESMERALDA69@GMAIL.COM</t>
+          <t>GUERRABERENICE34@MIAL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>11-02-2026 17:00:11</t>
+          <t>10-02-2026 16:49:08</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -10658,27 +10670,27 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>11-02-2026 17:05:02</t>
+          <t>18-02-2026 18:06:32</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>11-02-2026 17:04:20</t>
+          <t>18-02-2026 18:05:46</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -10698,36 +10710,40 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26080522270200002490</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr"/>
+          <t>26080522471390002879</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>343350</t>
+          <t>343142</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21167</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10737,17 +10753,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SOPHIA KENAI</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GARFIAS</t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SILVA</t>
+          <t xml:space="preserve"> AZPE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10757,67 +10773,75 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6462750693</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>6463062217</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>21-09-2007</t>
+          <t>14-06-1995</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>GRAFIAS12@GMAIL.COM</t>
+          <t>ESPINOZADAVID25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>12-02-2026 17:52:17</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 21:15:20</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>12-02-2026 17:53:33</t>
+          <t>11-02-2026 21:19:31</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>11-02-2026 21:19:04</t>
+        </is>
+      </c>
       <c r="U78" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10825,14 +10849,14 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26080522301000002563</t>
+          <t>26080522279400002518</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -10849,12 +10873,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>344412</t>
+          <t>343052</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22229</t>
+          <t>20869</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10864,17 +10888,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LIDIA</t>
+          <t xml:space="preserve">RUBI ESMERALDA </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t xml:space="preserve">CORTEZ </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -10884,7 +10908,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6461325931</t>
+          <t>6461323517</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10899,22 +10923,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>11-03-1959</t>
+          <t>07-02-1994</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>GONZALEZMONTALVO21377@GMAIL.COM</t>
+          <t>PONCEESMERALDA69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>17-02-2026 08:19:46</t>
+          <t>11-02-2026 17:00:11</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -10924,27 +10948,27 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>17-02-2026 08:22:04</t>
+          <t>11-02-2026 17:05:02</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>17-02-2026 08:21:38</t>
+          <t>11-02-2026 17:04:20</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -10964,19 +10988,19 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26080522421800002767</t>
+          <t>26080522270200002490</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -10988,12 +11012,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>344548</t>
+          <t>343350</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11003,17 +11027,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>SOPHIA KENAI</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>GARFIAS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DUARTE </t>
+          <t xml:space="preserve"> SILVA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11023,28 +11047,28 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6644916747</t>
+          <t>6462750693</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>11-02-1991</t>
+          <t>21-09-2007</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>MANUELMORENA23@GMAIL.COM</t>
+          <t>GRAFIAS12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>17-02-2026 16:07:21</t>
+          <t>12-02-2026 17:52:17</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11059,28 +11083,28 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>17-02-2026 16:08:29</t>
+          <t>12-02-2026 17:53:33</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V80" t="inlineStr"/>
@@ -11091,14 +11115,14 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26080522432990002792</t>
+          <t>26080522301000002563</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -11115,12 +11139,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>344877</t>
+          <t>344412</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11130,17 +11154,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JOSA</t>
+          <t>LIDIA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -11150,67 +11174,79 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3141475110</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>6461325931</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>15-11-2009</t>
+          <t>11-03-1959</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>JOSAGUTIERREZ@GMAIL.COM</t>
+          <t>GONZALEZMONTALVO21377@GMAIL.COM</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>18-02-2026 16:52:22</t>
+          <t>17-02-2026 08:19:46</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>18-02-2026 16:53:41</t>
+          <t>17-02-2026 08:22:04</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:21:38</t>
+        </is>
+      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W81" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11218,36 +11254,36 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>26080522467540002872</t>
+          <t>26080522421800002767</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>344091</t>
+          <t>344548</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11257,17 +11293,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMBARENA </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELGADO </t>
+          <t xml:space="preserve"> DUARTE </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -11277,57 +11313,53 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6461948652</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6644916747</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>06-09-2007</t>
+          <t>11-02-1991</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>VLARIALAMBARENA558@GMAIL.COM</t>
+          <t>MANUELMORENA23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>16-02-2026 14:19:45</t>
+          <t>17-02-2026 16:07:21</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>17-02-2026 13:22:02</t>
+          <t>17-02-2026 16:08:29</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -11335,21 +11367,13 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>17-02-2026 13:21:30</t>
-        </is>
-      </c>
+      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11357,27 +11381,19 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>26080522427660002779</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
-        </is>
-      </c>
+          <t>26080522432990002792</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -11389,12 +11405,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>345421</t>
+          <t>344877</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>87586</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11404,17 +11420,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t>JOSA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>VERGARA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11424,14 +11440,10 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6613327166</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>3141475110</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -11439,64 +11451,56 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>28-08-2012</t>
+          <t>15-11-2009</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>PEDROVERGARA55@GMAIL.COM</t>
+          <t>JOSAGUTIERREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>20-02-2026 20:44:02</t>
+          <t>18-02-2026 16:52:22</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>20-02-2026 20:50:55</t>
+          <t>18-02-2026 16:53:41</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>20-02-2026 20:50:08</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11504,22 +11508,308 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26080522537020003019</t>
+          <t>26080522467540002872</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>344091</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>21908</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VALERIA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAMBARENA </t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DELGADO </t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>6461948652</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>06-09-2007</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>VLARIALAMBARENA558@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:19:45</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>17-02-2026 13:22:02</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>17-02-2026 13:21:30</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>26080522427660002779</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>David Alejandro  Vasquez Felix</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>345421</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>87586</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEDRO </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>VERGARA</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PERALTA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>6613327166</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>28-08-2012</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>PEDROVERGARA55@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>20-02-2026 20:44:02</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>20-02-2026 20:50:55</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>20-02-2026 20:50:08</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>26080522537020003019</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
+      <c r="AC85" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
@@ -2877,12 +2877,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340168</t>
+          <t>341692</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAHI </t>
+          <t>JAIME ULISES</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZUÑIGA </t>
+          <t xml:space="preserve">LEON </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6461018157</t>
+          <t>6463868081</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2922,57 +2922,53 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16-07-1993</t>
+          <t>23-05-2002</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ZUARCE16@GMAIL.COM</t>
+          <t>LEONCHAPARRO1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 14:17:16</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 19:48:31</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 14:25:32</t>
+          <t>06-02-2026 19:53:01</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-02-2026 14:24:42</t>
+          <t>06-02-2026 19:52:22</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2982,7 +2978,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2992,14 +2988,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26080522012660001853</t>
+          <t>26080522147500002197</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3016,12 +3012,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341692</t>
+          <t>340168</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3031,17 +3027,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JAIME ULISES</t>
+          <t xml:space="preserve">SARAHI </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEON </t>
+          <t xml:space="preserve">ZUÑIGA </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3051,7 +3047,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6463868081</t>
+          <t>6461018157</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3061,53 +3057,57 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23-05-2002</t>
+          <t>16-07-1993</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>LEONCHAPARRO1@GMAIL.COM</t>
+          <t>ZUARCE16@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>06-02-2026 19:48:31</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>02-02-2026 14:17:16</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>06-02-2026 19:53:01</t>
+          <t>02-02-2026 14:25:32</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>06-02-2026 19:52:22</t>
+          <t>02-02-2026 14:24:42</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26080522147500002197</t>
+          <t>26080522012660001853</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3278,12 +3278,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>294705</t>
+          <t>337214</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>92203</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3293,17 +3293,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RAMON HECTOR</t>
+          <t xml:space="preserve">LILIANA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESNEY </t>
+          <t>AMPARANO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AMPARANO</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6497822649</t>
+          <t>6462108123</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3328,24 +3328,20 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11-11-1984</t>
+          <t>30-03-1975</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>QUENESY_REF@HOTMAIL.COM</t>
+          <t>ARAMIREZ771@TGMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25-05-2025 13:22:47</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>23-01-2026 11:15:39</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3363,17 +3359,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>26-02-2026 18:41:56</t>
+          <t>06-02-2026 10:45:48</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>26-02-2026 18:41:11</t>
+          <t>06-02-2026 10:44:57</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3383,7 +3379,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3393,7 +3389,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26080522693430003362</t>
+          <t>26080522133760002160</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3405,24 +3401,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342189</t>
+          <t>294705</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>92203</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3432,17 +3428,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HENRY JOSE </t>
+          <t>RAMON HECTOR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t xml:space="preserve">QUESNEY </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>AMPARANO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3452,67 +3448,79 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6461439409</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6497822649</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10-03-1985</t>
+          <t>11-11-1984</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CHAVEZMORALES1@GMAIL.COM</t>
+          <t>QUENESY_REF@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:49</t>
+          <t>25-05-2025 13:22:47</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 14:46:17</t>
+          <t>26-02-2026 18:41:56</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>26-02-2026 18:41:11</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3520,36 +3528,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26080522193810002291</t>
+          <t>26080522693430003362</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342259</t>
+          <t>342189</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3559,17 +3567,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t xml:space="preserve">HENRY JOSE </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAUTISTA </t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3579,32 +3587,28 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6461486212</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461439409</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17-02-1985</t>
+          <t>10-03-1985</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BAUTISTAGONZALEZ1@GMAIL.COM</t>
+          <t>CHAVEZMORALES1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:33:32</t>
+          <t>09-02-2026 14:44:49</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3614,44 +3618,36 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:38:00</t>
+          <t>09-02-2026 14:46:17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>09-02-2026 16:37:17</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3659,36 +3655,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26080522198950002301</t>
+          <t>26080522193810002291</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>337214</t>
+          <t>342259</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3698,17 +3694,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LILIANA </t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AMPARANO</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t xml:space="preserve">BAUTISTA </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3718,7 +3714,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6462108123</t>
+          <t>6461486212</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3733,48 +3729,52 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30-03-1975</t>
+          <t>17-02-1985</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ARAMIREZ771@TGMAIL.COM</t>
+          <t>BAUTISTAGONZALEZ1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>23-01-2026 11:15:39</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>09-02-2026 16:33:32</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>06-02-2026 10:45:48</t>
+          <t>09-02-2026 16:38:00</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>06-02-2026 10:44:57</t>
+          <t>09-02-2026 16:37:17</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3794,24 +3794,24 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26080522133760002160</t>
+          <t>26080522198950002301</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4346,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342712</t>
+          <t>339888</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIA VALERIA </t>
+          <t xml:space="preserve">CAROLINA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6161246640</t>
+          <t>6461281526</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DEL ROBLE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4396,22 +4396,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-01-2005</t>
+          <t>19-09-1997</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MIAGUERRA54@GMAIL.COM</t>
+          <t>MUSIKARO8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10-02-2026 16:32:54</t>
+          <t>02-02-2026 07:54:47</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4421,27 +4421,27 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>23-02-2026 18:56:39</t>
+          <t>02-02-2026 08:00:19</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>23-02-2026 18:56:01</t>
+          <t>02-02-2026 07:58:28</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4461,40 +4461,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26080522597810003114</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522000340001820</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342826</t>
+          <t>342712</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20529</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4504,17 +4500,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA KARINA </t>
+          <t xml:space="preserve">MIA VALERIA </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4524,12 +4520,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6461910901</t>
+          <t>6161246640</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DEL ROBLE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4539,22 +4535,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>02-01-2005</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>SANDYO0O0O0O0O0O0O0@GMAIL.COM</t>
+          <t>MIAGUERRA54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 19:09:54</t>
+          <t>10-02-2026 16:32:54</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4564,27 +4560,27 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>26-02-2026 21:19:12</t>
+          <t>23-02-2026 18:56:39</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>26-02-2026 21:18:36</t>
+          <t>23-02-2026 18:56:01</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4594,7 +4590,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4604,22 +4600,18 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26080522697350003376</t>
+          <t>26080522597810003114</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4636,12 +4628,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>341021</t>
+          <t>342826</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4651,17 +4643,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA </t>
+          <t xml:space="preserve">SANDRA KARINA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TOLEDO</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4671,10 +4663,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6623276252</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6461910901</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4682,17 +4678,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>29-08-2006</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>SANDOVAL1@GMAIL.COM</t>
+          <t>SANDYO0O0O0O0O0O0O0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>04-02-2026 14:49:52</t>
+          <t>10-02-2026 19:09:54</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4702,36 +4698,44 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>04-02-2026 14:52:30</t>
+          <t>26-02-2026 21:19:12</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>26-02-2026 21:18:36</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4739,19 +4743,27 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26080522076440002031</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26080522697350003376</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4763,12 +4775,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>339888</t>
+          <t>341021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4778,17 +4790,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAROLINA </t>
+          <t xml:space="preserve">VICTORIA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TOLEDO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4798,14 +4810,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6461281526</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6623276252</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4813,17 +4821,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19-09-1997</t>
+          <t>29-08-2006</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MUSIKARO8@GMAIL.COM</t>
+          <t>SANDOVAL1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-02-2026 07:54:47</t>
+          <t>04-02-2026 14:49:52</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4833,12 +4841,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4848,29 +4856,21 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-02-2026 08:00:19</t>
+          <t>04-02-2026 14:52:30</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>02-02-2026 07:58:28</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26080522000340001820</t>
+          <t>26080522076440002031</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5438,12 +5438,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340546</t>
+          <t>343520</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>21337</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMA KARINA </t>
+          <t>IRISS ANNELIS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve"> OCHOA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5473,14 +5473,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6462760004</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>AVENIDA DE LAS AMÉRICAS 796</t>
-        </is>
-      </c>
+          <t>6648515854</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5488,60 +5484,56 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>03-04-1997</t>
+          <t>22-05-2007</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ALMAH2778@GMAIL.CON</t>
+          <t>RAMIREZIRISS23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-02-2026 12:27:28</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>13-02-2026 15:45:04</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>03-02-2026 12:27:29</t>
+          <t>13-02-2026 15:47:14</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:27:29</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5549,19 +5541,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26080522038410001925</t>
+          <t>26080522323130002622</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Aaron Felipe Aguilar Grave</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5573,12 +5565,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340591</t>
+          <t>340199</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5588,17 +5580,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRIAM LINETH </t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5608,28 +5600,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3111583964</t>
+          <t>6463458118</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>04-10-1999</t>
+          <t>04-03-2006</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ROMEROOCHOA1@GMAIL.COM</t>
+          <t>VEGAPELAYO1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>03-02-2026 14:18:11</t>
+          <t>02-02-2026 15:04:45</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5644,28 +5636,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>03-02-2026 14:19:50</t>
+          <t>02-02-2026 15:06:10</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5676,14 +5668,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26080522040970001933</t>
+          <t>26080522013810001858</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5700,12 +5692,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343520</t>
+          <t>340546</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21337</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5715,17 +5707,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IRISS ANNELIS</t>
+          <t xml:space="preserve">ALMA KARINA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OCHOA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5735,10 +5727,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6648515854</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6462760004</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AVENIDA DE LAS AMÉRICAS 796</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5746,56 +5742,60 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>22-05-2007</t>
+          <t>03-04-1997</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>RAMIREZIRISS23@GMAIL.COM</t>
+          <t>ALMAH2778@GMAIL.CON</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13-02-2026 15:45:04</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 12:27:28</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>13-02-2026 15:47:14</t>
+          <t>03-02-2026 12:27:29</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>03-02-2026 12:27:29</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5803,19 +5803,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26080522323130002622</t>
+          <t>26080522038410001925</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5827,12 +5827,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340812</t>
+          <t>340591</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5842,17 +5842,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t xml:space="preserve">MIRIAM LINETH </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CARDOSO</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5862,32 +5862,28 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6461504499</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>3111583964</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30-08-1993</t>
+          <t>04-10-1999</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>RUBENCARDOSO@GMAIL.COM</t>
+          <t>ROMEROOCHOA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-02-2026 19:20:39</t>
+          <t>03-02-2026 14:18:11</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5897,22 +5893,22 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>03-02-2026 19:27:16</t>
+          <t>03-02-2026 14:19:50</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5920,21 +5916,13 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>03-02-2026 19:26:45</t>
-        </is>
-      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5942,14 +5930,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26080522056050001974</t>
+          <t>26080522040970001933</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5966,12 +5954,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340199</t>
+          <t>340396</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5981,17 +5969,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t xml:space="preserve">ARGENIS ISRAEL </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6001,7 +5989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6463458118</t>
+          <t>6462867842</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6012,17 +6000,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>04-03-2006</t>
+          <t>12-05-2005</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>VEGAPELAYO1@GMAIL.COM</t>
+          <t>GONZALEZARGENIS1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>02-02-2026 15:04:45</t>
+          <t>02-02-2026 20:56:58</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6047,7 +6035,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>02-02-2026 15:06:10</t>
+          <t>02-02-2026 20:59:14</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6069,7 +6057,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26080522013810001858</t>
+          <t>26080522023520001895</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6081,24 +6069,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>341836</t>
+          <t>340812</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6108,17 +6096,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIREYA DEL ROSARIO </t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLLANTES </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>CARDOSO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6128,28 +6116,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6461505249</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6461504499</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>25-09-1958</t>
+          <t>30-08-1993</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>COLLANTES1@GMAIL.COM</t>
+          <t>RUBENCARDOSO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>07-02-2026 13:55:26</t>
+          <t>03-02-2026 19:20:39</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6159,36 +6151,44 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>07-02-2026 13:57:17</t>
+          <t>03-02-2026 19:27:16</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>03-02-2026 19:26:45</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6196,36 +6196,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26080522161990002219</t>
+          <t>26080522056050001974</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>342000</t>
+          <t>341836</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6235,17 +6235,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t xml:space="preserve">MIREYA DEL ROSARIO </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t xml:space="preserve">COLLANTES </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6255,75 +6255,67 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6463423633</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461505249</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>16-11-2007</t>
+          <t>25-09-1958</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ALBERTOESTRARODRI12@GMAIL.COM</t>
+          <t>COLLANTES1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>09-02-2026 05:38:00</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>07-02-2026 13:55:26</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>09-02-2026 05:41:17</t>
+          <t>07-02-2026 13:57:17</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>09-02-2026 05:40:26</t>
-        </is>
-      </c>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6331,19 +6323,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26080522180720002239</t>
+          <t>26080522161990002219</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6355,12 +6347,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>340396</t>
+          <t>342000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6370,17 +6362,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGENIS ISRAEL </t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6390,10 +6382,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6462867842</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6463423633</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6401,56 +6397,60 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>12-05-2005</t>
+          <t>16-11-2007</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>GONZALEZARGENIS1@GMAIL.COM</t>
+          <t>ALBERTOESTRARODRI12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:58</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 05:38:00</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>02-02-2026 20:59:14</t>
+          <t>09-02-2026 05:41:17</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>09-02-2026 05:40:26</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6458,14 +6458,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26080522023520001895</t>
+          <t>26080522180720002239</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6482,12 +6482,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>340829</t>
+          <t>340356</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6497,17 +6497,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JOVANA</t>
+          <t xml:space="preserve">PAULINA LIZETH </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LARIOS</t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t xml:space="preserve"> MERCADO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6461276781</t>
+          <t>6243206497</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6528,17 +6528,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>24-07-1989</t>
+          <t>22-06-2006</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>JOVANALARIOS13@GMAIL.COM</t>
+          <t>PAULINACESEÑA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>03-02-2026 20:04:47</t>
+          <t>02-02-2026 18:54:50</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6553,22 +6553,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>03-02-2026 20:06:10</t>
+          <t>02-02-2026 18:56:21</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -6585,36 +6585,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26080522057330001981</t>
+          <t>26080522021340001884</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>340918</t>
+          <t>340388</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>18206</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6624,17 +6624,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MARIANA ELIDE</t>
+          <t xml:space="preserve">VICTOR GERARDO </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLACENCIA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6644,67 +6644,75 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6462372600</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6462866658</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>12-08-2002</t>
+          <t>28-05-1998</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MAELGUZ1997@GMAIL.COM</t>
+          <t>VICTORCOTA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>04-02-2026 09:40:41</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 20:29:45</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>04-02-2026 09:42:07</t>
+          <t>02-02-2026 20:54:24</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>02-02-2026 20:45:22</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6712,19 +6720,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26080522070810002008</t>
+          <t>26080522023450001894</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Aaron Felipe Aguilar Grave</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6736,12 +6744,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>340965</t>
+          <t>341096</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6751,17 +6759,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROBERTO </t>
+          <t>ADAN ALEJANDRO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">ROBLES </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6771,10 +6779,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6461514504</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6461017657</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6782,42 +6794,38 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>07-06-1962</t>
+          <t>30-09-1990</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>RHG6206@HOTMAIL.COM</t>
+          <t>ADANROBLES1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>04-02-2026 12:21:43</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 17:07:45</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>04-02-2026 12:23:09</t>
+          <t>04-02-2026 17:13:37</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6825,13 +6833,21 @@
           <t>04-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>04-02-2026 17:13:04</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6839,36 +6855,36 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26080522073340002018</t>
+          <t>26080522081730002044</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>340356</t>
+          <t>340829</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6878,17 +6894,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULINA LIZETH </t>
+          <t>JOVANA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CESEÑA</t>
+          <t>LARIOS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MERCADO</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6898,7 +6914,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6243206497</t>
+          <t>6461276781</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6909,17 +6925,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>22-06-2006</t>
+          <t>24-07-1989</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PAULINACESEÑA1@GMAIL.COM</t>
+          <t>JOVANALARIOS13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>02-02-2026 18:54:50</t>
+          <t>03-02-2026 20:04:47</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6934,22 +6950,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>02-02-2026 18:56:21</t>
+          <t>03-02-2026 20:06:10</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -6966,36 +6982,36 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26080522021340001884</t>
+          <t>26080522057330001981</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>340388</t>
+          <t>340918</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7005,17 +7021,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR GERARDO </t>
+          <t>MARIANA ELIDE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">PLACENCIA </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7025,75 +7041,67 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6462866658</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462372600</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>28-05-1998</t>
+          <t>12-08-2002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>VICTORCOTA1@GMAIL.COM</t>
+          <t>MAELGUZ1997@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>02-02-2026 20:29:45</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>04-02-2026 09:40:41</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>02-02-2026 20:54:24</t>
+          <t>04-02-2026 09:42:07</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>02-02-2026 20:45:22</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7101,19 +7109,19 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26080522023450001894</t>
+          <t>26080522070810002008</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7125,12 +7133,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>340969</t>
+          <t>340965</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7140,17 +7148,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t xml:space="preserve">ROBERTO </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GLAVEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7160,7 +7168,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6562453111</t>
+          <t>6461514504</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7171,17 +7179,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17-09-1994</t>
+          <t>07-06-1962</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>VGALVEZVARGAS@GMAIL.COM</t>
+          <t>RHG6206@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>04-02-2026 12:28:52</t>
+          <t>04-02-2026 12:21:43</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7206,7 +7214,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>04-02-2026 12:29:56</t>
+          <t>04-02-2026 12:23:09</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7228,7 +7236,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26080522073480002020</t>
+          <t>26080522073340002018</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7252,12 +7260,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>341096</t>
+          <t>344671</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7267,17 +7275,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ADAN ALEJANDRO</t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROBLES </t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t xml:space="preserve"> BADILLO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7287,7 +7295,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6461017657</t>
+          <t>6461191119</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7302,20 +7310,24 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30-09-1990</t>
+          <t>13-07-1996</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ADANROBLES1@GMAIL.COM</t>
+          <t>ANTONIOVALBADILLO234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>04-02-2026 17:07:45</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>17-02-2026 18:55:18</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7323,27 +7335,27 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>04-02-2026 17:13:37</t>
+          <t>17-02-2026 19:00:16</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>04-02-2026 17:13:04</t>
+          <t>17-02-2026 18:59:28</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7353,7 +7365,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7363,19 +7375,19 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26080522081730002044</t>
+          <t>26080522443150002818</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Aaron Felipe Aguilar Grave</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7387,12 +7399,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344671</t>
+          <t>340969</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7402,17 +7414,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>GLAVEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BADILLO</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7422,14 +7434,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6461191119</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6562453111</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7437,17 +7445,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>13-07-1996</t>
+          <t>17-09-1994</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ANTONIOVALBADILLO234@GMAIL.COM</t>
+          <t>VGALVEZVARGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17-02-2026 18:55:18</t>
+          <t>04-02-2026 12:28:52</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7457,44 +7465,36 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>17-02-2026 19:00:16</t>
+          <t>04-02-2026 12:29:56</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>17-02-2026 18:59:28</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7502,24 +7502,24 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26080522443150002818</t>
+          <t>26080522073480002020</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7653,12 +7653,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>341153</t>
+          <t>341959</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7668,17 +7668,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA </t>
+          <t xml:space="preserve">SADDAM SILVESTRE </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">RANGEL </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7688,28 +7688,28 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6461483552</t>
+          <t>6461368664</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>27-08-2007</t>
+          <t>15-12-1992</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>RANGELGUZMAN1@GMAIL.COM</t>
+          <t>SOTOAGUIRRE45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>04-02-2026 18:44:51</t>
+          <t>08-02-2026 14:28:04</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7724,28 +7724,28 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>04-02-2026 18:45:48</t>
+          <t>08-02-2026 14:29:08</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>08-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V55" t="inlineStr"/>
@@ -7756,36 +7756,36 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26080522086240002050</t>
+          <t>26080522173030002231</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344305</t>
+          <t>341999</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7795,17 +7795,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>REINA KETZALLI</t>
+          <t>TANIA JASMIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BANDA</t>
+          <t xml:space="preserve">ESTRADA </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESPINOZA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7815,10 +7815,14 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6151551917</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>6461874843</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7826,56 +7830,60 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>09-11-2007</t>
+          <t>02-08-1984</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>REINABANDA55@GMAIL.COM</t>
+          <t>TANIAESTRADA797@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16-02-2026 18:39:30</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 05:30:17</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>16-02-2026 18:41:01</t>
+          <t>09-02-2026 05:36:30</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>09-02-2026 05:35:38</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7883,19 +7891,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26080522405320002747</t>
+          <t>26080522180640002238</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7907,12 +7915,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>341959</t>
+          <t>344305</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7922,17 +7930,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">SADDAM SILVESTRE </t>
+          <t>REINA KETZALLI</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>BANDA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t xml:space="preserve"> ESPINOZA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7942,28 +7950,28 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6461368664</t>
+          <t>6151551917</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>15-12-1992</t>
+          <t>09-11-2007</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>SOTOAGUIRRE45@GMAIL.COM</t>
+          <t>REINABANDA55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>08-02-2026 14:28:04</t>
+          <t>16-02-2026 18:39:30</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -7978,22 +7986,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>08-02-2026 14:29:08</t>
+          <t>16-02-2026 18:41:01</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>08-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -8010,19 +8018,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26080522173030002231</t>
+          <t>26080522405320002747</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Aaron Felipe Aguilar Grave</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8034,12 +8042,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>341999</t>
+          <t>341153</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8049,17 +8057,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TANIA JASMIN</t>
+          <t xml:space="preserve">DANIA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTRADA </t>
+          <t xml:space="preserve">RANGEL </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8069,14 +8077,10 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6461874843</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461483552</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8084,60 +8088,56 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>02-08-1984</t>
+          <t>27-08-2007</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>TANIAESTRADA797@GMAIL.COM</t>
+          <t>RANGELGUZMAN1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>09-02-2026 05:30:17</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>04-02-2026 18:44:51</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>09-02-2026 05:36:30</t>
+          <t>04-02-2026 18:45:48</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>09-02-2026 05:35:38</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8145,36 +8145,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26080522180640002238</t>
+          <t>26080522086240002050</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344526</t>
+          <t>342133</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8184,17 +8184,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JOSE CARLO</t>
+          <t>YASMIN CAROLINA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t xml:space="preserve">LARA </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8204,28 +8204,32 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6469478205</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>6462272759</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>09-03-2009</t>
+          <t>08-02-1987</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>GALVANJC66@GMAIL.COM</t>
+          <t>YASMIN.CLR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>17-02-2026 15:22:33</t>
+          <t>09-02-2026 12:27:09</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8235,36 +8239,44 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>17-02-2026 15:23:39</t>
+          <t>09-02-2026 12:31:24</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>09-02-2026 12:30:44</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8272,36 +8284,36 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26080522431360002789</t>
+          <t>26080522190470002279</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342338</t>
+          <t>344526</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8311,17 +8323,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DANIEL EDUARDO</t>
+          <t>JOSE CARLO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HUICAB</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8331,7 +8343,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>9811592635</t>
+          <t>6469478205</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8342,17 +8354,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>23-02-1998</t>
+          <t>09-03-2009</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>DANIELHUICAB@GMAIL.COM</t>
+          <t>GALVANJC66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:39</t>
+          <t>17-02-2026 15:22:33</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8367,22 +8379,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>09-02-2026 17:36:58</t>
+          <t>17-02-2026 15:23:39</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -8399,36 +8411,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26080522203080002312</t>
+          <t>26080522431360002789</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>342133</t>
+          <t>342338</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>20156</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8438,17 +8450,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>YASMIN CAROLINA</t>
+          <t>DANIEL EDUARDO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LARA </t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>HUICAB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8458,32 +8470,28 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6462272759</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>9811592635</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>08-02-1987</t>
+          <t>23-02-1998</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>YASMIN.CLR@GMAIL.COM</t>
+          <t>DANIELHUICAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>09-02-2026 12:27:09</t>
+          <t>09-02-2026 17:35:39</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8493,22 +8501,22 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>09-02-2026 12:31:24</t>
+          <t>09-02-2026 17:36:58</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -8516,21 +8524,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>09-02-2026 12:30:44</t>
-        </is>
-      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8538,19 +8538,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26080522190470002279</t>
+          <t>26080522203080002312</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8562,12 +8562,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>342456</t>
+          <t>346145</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>88310</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8577,17 +8577,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL GERMAN </t>
+          <t xml:space="preserve">ABEL </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>AMADOR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6461289040</t>
+          <t>6463423558</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8608,22 +8608,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>02-01-1998</t>
+          <t>05-10-2006</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>MRAMOST98@HOTMAIL.COM</t>
+          <t>ABELAMADOR721@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>09-02-2026 19:48:26</t>
+          <t>24-02-2026 13:03:28</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>09-02-2026 19:50:37</t>
+          <t>24-02-2026 13:04:48</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26080522212170002344</t>
+          <t>26080522618520003171</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -8677,24 +8677,24 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>342644</t>
+          <t>342456</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8704,17 +8704,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ANAIS</t>
+          <t xml:space="preserve">MIGUEL GERMAN </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8724,28 +8724,28 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6463836075</t>
+          <t>6461289040</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>27-06-1995</t>
+          <t>02-01-1998</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ANAIS.GUZMAN166@GMAIL.COM</t>
+          <t>MRAMOST98@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>10-02-2026 14:38:51</t>
+          <t>09-02-2026 19:48:26</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8760,28 +8760,28 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>10-02-2026 14:40:07</t>
+          <t>09-02-2026 19:50:37</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V63" t="inlineStr"/>
@@ -8792,19 +8792,19 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26080522232960002400</t>
+          <t>26080522212170002344</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8816,12 +8816,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>342723</t>
+          <t>342644</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8831,17 +8831,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RAFAEL LEONARDO</t>
+          <t>ANAIS</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8851,79 +8851,67 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6421374093</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6463836075</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>20-11-2010</t>
+          <t>27-06-1995</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>LEONARDOGUERRA12@GMAIL.COM</t>
+          <t>ANAIS.GUZMAN166@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>10-02-2026 16:50:19</t>
+          <t>10-02-2026 14:38:51</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:12:04</t>
+          <t>10-02-2026 14:40:07</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:11:28</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8931,18 +8919,14 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26080522471680002882</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522232960002400</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -8959,12 +8943,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>346145</t>
+          <t>342723</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>88310</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8974,17 +8958,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABEL </t>
+          <t>RAFAEL LEONARDO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AMADOR</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8994,10 +8978,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6463423558</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>6421374093</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9005,56 +8993,64 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>05-10-2006</t>
+          <t>20-11-2010</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ABELAMADOR721@GMAIL.COM</t>
+          <t>LEONARDOGUERRA12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>24-02-2026 13:03:28</t>
+          <t>10-02-2026 16:50:19</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>24-02-2026 13:04:48</t>
+          <t>18-02-2026 18:12:04</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:11:28</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9062,14 +9058,18 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26080522618520003171</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr"/>
+          <t>26080522471680002882</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9086,12 +9086,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345392</t>
+          <t>346584</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>87557</t>
+          <t>88749</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9101,17 +9101,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PAULINA ABRIL</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>TINOCO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9121,67 +9121,79 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6461024876</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6461430132</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>11-09-1996</t>
+          <t>18-04-1981</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>PAULINAABRIL45@GMAIL.COM</t>
+          <t>SALVADORSANCHEZ01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:27:25</t>
+          <t>25-02-2026 19:16:31</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:29:17</t>
+          <t>25-02-2026 19:28:52</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>25-02-2026 19:28:14</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9189,14 +9201,14 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26080522534310003010</t>
+          <t>26080522666180003306</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -9213,12 +9225,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>342711</t>
+          <t>345392</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>87557</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9228,17 +9240,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL LEONARDO </t>
+          <t>PAULINA ABRIL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>URBINA</t>
+          <t xml:space="preserve"> PAZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9248,79 +9260,67 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6161070933</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461024876</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>07-12-1978</t>
+          <t>11-09-1996</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>FELIXUBINA66@GMAIL.COM</t>
+          <t>PAULINAABRIL45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>10-02-2026 16:32:25</t>
+          <t>20-02-2026 18:27:25</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:47</t>
+          <t>20-02-2026 18:29:17</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:14:19</t>
-        </is>
-      </c>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9328,18 +9328,14 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26080522471840002883</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522534310003010</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9356,12 +9352,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>343823</t>
+          <t>346937</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21640</t>
+          <t>89102</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9371,17 +9367,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS ENRIQUE </t>
+          <t>ROBERTO JETZHAYN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>TIRADO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RABAGO</t>
+          <t>CARRAZCO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9391,14 +9387,10 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6462156247</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461411494</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9406,60 +9398,56 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>10-12-1998</t>
+          <t>14-04-1981</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>JESUSCRUZ67@GMAIL.COM</t>
+          <t>JETZHAYN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>15-02-2026 11:56:03</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>27-02-2026 12:52:21</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>15-02-2026 12:01:14</t>
+          <t>27-02-2026 12:54:41</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>15-02-2026 12:00:45</t>
-        </is>
-      </c>
+          <t>27-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9467,36 +9455,36 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26080522365020002662</t>
+          <t>26080522710670003403</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>346584</t>
+          <t>347013</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88749</t>
+          <t>89178</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9506,17 +9494,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>ISAMAR YOHARI</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TINOCO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9526,32 +9514,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6461430132</t>
+          <t>6465856584</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ALISOS 54</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18-04-1981</t>
+          <t>11-12-2010</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>SALVADORSANCHEZ01@GMAIL.COM</t>
+          <t>ISAMARYOHARI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>25-02-2026 19:16:31</t>
+          <t>27-02-2026 17:09:41</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9576,17 +9564,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>25-02-2026 19:28:52</t>
+          <t>27-02-2026 17:16:19</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>25-02-2026 19:28:14</t>
+          <t>27-02-2026 17:15:09</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9606,7 +9594,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26080522666180003306</t>
+          <t>26080522720120003416</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9630,12 +9618,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>343185</t>
+          <t>342711</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9645,17 +9633,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FERNANDA CELIA</t>
+          <t xml:space="preserve">RAFAEL LEONARDO </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARAUJO </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>URBINA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9665,35 +9653,39 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6463842082</t>
+          <t>6161070933</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>BAHIA MAGADALENA 313</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>10-04-2002</t>
+          <t>07-12-1978</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>FERNADNACELIAARAUJOLOPEZ@HOTMAIL.COM</t>
+          <t>FELIXUBINA66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>12-02-2026 08:40:25</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>10-02-2026 16:32:25</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9711,17 +9703,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>12-02-2026 08:45:43</t>
+          <t>18-02-2026 18:14:47</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>12-02-2026 08:45:03</t>
+          <t>18-02-2026 18:14:19</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9741,10 +9733,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26080522289620002530</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr"/>
+          <t>26080522471840002883</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
@@ -9753,24 +9749,24 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343142</t>
+          <t>343185</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9780,17 +9776,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>FERNANDA CELIA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t xml:space="preserve">ARAUJO </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AZPE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9800,32 +9796,32 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6463062217</t>
+          <t>6463842082</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BAHIA MAGADALENA 313</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>14-06-1995</t>
+          <t>10-04-2002</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ESPINOZADAVID25@GMAIL.COM</t>
+          <t>FERNADNACELIAARAUJOLOPEZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>11-02-2026 21:15:20</t>
+          <t>12-02-2026 08:40:25</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9846,17 +9842,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>11-02-2026 21:19:31</t>
+          <t>12-02-2026 08:45:43</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>11-02-2026 21:19:04</t>
+          <t>12-02-2026 08:45:03</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9876,7 +9872,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26080522279400002518</t>
+          <t>26080522289620002530</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -9900,12 +9896,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>346937</t>
+          <t>343823</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>89102</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9915,17 +9911,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ROBERTO JETZHAYN</t>
+          <t xml:space="preserve">JESUS ENRIQUE </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TIRADO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CARRAZCO</t>
+          <t>RABAGO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9935,10 +9931,14 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6461411494</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>6462156247</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9946,56 +9946,60 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>14-04-1981</t>
+          <t>10-12-1998</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>JETZHAYN@GMAIL.COM</t>
+          <t>JESUSCRUZ67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>27-02-2026 12:52:21</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 11:56:03</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>27-02-2026 12:54:41</t>
+          <t>15-02-2026 12:01:14</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>27-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>15-02-2026 12:00:45</t>
+        </is>
+      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10003,36 +10007,36 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26080522710670003403</t>
+          <t>26080522365020002662</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>347013</t>
+          <t>343142</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10042,17 +10046,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ISAMAR YOHARI</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve"> AZPE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10062,39 +10066,35 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6465856584</t>
+          <t>6463062217</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ALISOS 54</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>11-12-2010</t>
+          <t>14-06-1995</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ISAMARYOHARI@GMAIL.COM</t>
+          <t>ESPINOZADAVID25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>27-02-2026 17:09:41</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 21:15:20</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10112,17 +10112,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>27-02-2026 17:16:19</t>
+          <t>11-02-2026 21:19:31</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>27-02-2026 17:15:09</t>
+          <t>11-02-2026 21:19:04</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26080522720120003416</t>
+          <t>26080522279400002518</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
@@ -10154,24 +10154,24 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>343351</t>
+          <t>343812</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10181,17 +10181,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>JOSE MARIA</t>
+          <t xml:space="preserve">ENRIQUE CESAR </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GARFIAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10201,10 +10201,14 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6462677544</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>6461505634</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10212,56 +10216,60 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>04-05-2009</t>
+          <t>15-06-1973</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>GARFIASSILVA.JOSE@GMAIL.COM</t>
+          <t>SANCHEZGARCIAS65@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>12-02-2026 17:52:23</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 11:24:34</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>12-02-2026 17:53:22</t>
+          <t>15-02-2026 11:27:07</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:26:42</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10269,19 +10277,19 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26080522300960002562</t>
+          <t>26080522364410002661</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -10293,12 +10301,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>343448</t>
+          <t>343351</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10308,17 +10316,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NELLY</t>
+          <t>JOSE MARIA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>GARFIAS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10328,75 +10336,67 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6461980165</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>LAZARO CARDENAS</t>
-        </is>
-      </c>
+          <t>6462677544</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>08-12-1978</t>
+          <t>04-05-2009</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>NELLYRAMIREZ25@HOTMAIL.COM</t>
+          <t>GARFIASSILVA.JOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>13-02-2026 09:32:16</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>12-02-2026 17:52:23</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>13-02-2026 09:38:42</t>
+          <t>12-02-2026 17:53:22</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>13-02-2026 09:37:53</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10404,14 +10404,14 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26080522317600002604</t>
+          <t>26080522300960002562</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -10428,12 +10428,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>342722</t>
+          <t>343448</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BERENICE</t>
+          <t>NELLY</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6469475604</t>
+          <t>6461980165</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LAZARO CARDENAS</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10478,24 +10478,20 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>24-02-1978</t>
+          <t>08-12-1978</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>GUERRABERENICE34@MIAL.COM</t>
+          <t>NELLYRAMIREZ25@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>10-02-2026 16:49:08</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 09:32:16</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10513,17 +10509,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>18-02-2026 18:06:32</t>
+          <t>13-02-2026 09:38:42</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>18-02-2026 18:05:46</t>
+          <t>13-02-2026 09:37:53</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10543,14 +10539,10 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26080522471390002879</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522317600002604</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
@@ -10559,24 +10551,24 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>343812</t>
+          <t>342722</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10586,12 +10578,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUE CESAR </t>
+          <t>BERENICE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -10606,7 +10598,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6461505634</t>
+          <t>6469475604</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -10616,25 +10608,29 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>15-06-1973</t>
+          <t>24-02-1978</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>SANCHEZGARCIAS65@GMAIL.COM</t>
+          <t>GUERRABERENICE34@MIAL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>15-02-2026 11:24:34</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>10-02-2026 16:49:08</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10652,17 +10648,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>15-02-2026 11:27:07</t>
+          <t>18-02-2026 18:06:32</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>15-02-2026 11:26:42</t>
+          <t>18-02-2026 18:05:46</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -10682,10 +10678,14 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26080522364410002661</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr"/>
+          <t>26080522471390002879</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
@@ -10694,24 +10694,24 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>343052</t>
+          <t>343861</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20869</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10721,17 +10721,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBI ESMERALDA </t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTEZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6461323517</t>
+          <t>6462611759</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10756,22 +10756,22 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>07-02-1994</t>
+          <t>08-11-1986</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>PONCEESMERALDA69@GMAIL.COM</t>
+          <t>LF3456648@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>11-02-2026 17:00:11</t>
+          <t>15-02-2026 13:55:03</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -10781,27 +10781,27 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>11-02-2026 17:05:02</t>
+          <t>17-02-2026 17:45:02</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>11-02-2026 17:04:20</t>
+          <t>17-02-2026 17:44:20</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -10821,14 +10821,14 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26080522270200002490</t>
+          <t>26080522438690002809</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -10845,12 +10845,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>343861</t>
+          <t>343052</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>20869</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10860,17 +10860,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t xml:space="preserve">RUBI ESMERALDA </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">CORTEZ </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6462611759</t>
+          <t>6461323517</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10895,22 +10895,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>08-11-1986</t>
+          <t>07-02-1994</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>LF3456648@GMAIL.COM</t>
+          <t>PONCEESMERALDA69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>15-02-2026 13:55:03</t>
+          <t>11-02-2026 17:00:11</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -10920,27 +10920,27 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>17-02-2026 17:45:02</t>
+          <t>11-02-2026 17:05:02</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>17-02-2026 17:44:20</t>
+          <t>11-02-2026 17:04:20</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -10960,14 +10960,14 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26080522438690002809</t>
+          <t>26080522270200002490</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -10984,12 +10984,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>344601</t>
+          <t>344412</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -10999,17 +10999,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIN DE JESUS </t>
+          <t>LIDIA</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11019,67 +11019,79 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6462247390</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>6461325931</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>22-01-1992</t>
+          <t>11-03-1959</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>RAMIREZBRACO554@GMAIL.COM</t>
+          <t>GONZALEZMONTALVO21377@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>17-02-2026 17:19:31</t>
+          <t>17-02-2026 08:19:46</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>19-02-2026 17:18:11</t>
+          <t>17-02-2026 08:22:04</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:21:38</t>
+        </is>
+      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W80" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11087,32 +11099,24 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26080522500880002947</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
-        </is>
-      </c>
+          <t>26080522421800002767</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -11266,12 +11270,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>343350</t>
+          <t>344548</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21167</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11281,17 +11285,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SOPHIA KENAI</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GARFIAS</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SILVA</t>
+          <t xml:space="preserve"> DUARTE </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -11301,28 +11305,28 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6462750693</t>
+          <t>6644916747</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>21-09-2007</t>
+          <t>11-02-1991</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>GRAFIAS12@GMAIL.COM</t>
+          <t>MANUELMORENA23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>12-02-2026 17:52:17</t>
+          <t>17-02-2026 16:07:21</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11337,28 +11341,28 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>12-02-2026 17:53:33</t>
+          <t>17-02-2026 16:08:29</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V82" t="inlineStr"/>
@@ -11369,14 +11373,14 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>26080522301000002563</t>
+          <t>26080522432990002792</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
@@ -11393,12 +11397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>344412</t>
+          <t>344410</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22229</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11408,17 +11412,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LIDIA</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11428,7 +11432,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6461325931</t>
+          <t>6461298989</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -11443,17 +11447,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>11-03-1959</t>
+          <t>24-05-1956</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>GONZALEZMONTALVO21377@GMAIL.COM</t>
+          <t>PADILLARAQUEL45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>17-02-2026 08:19:46</t>
+          <t>17-02-2026 08:14:06</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11478,7 +11482,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>17-02-2026 08:22:04</t>
+          <t>17-02-2026 08:18:21</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -11488,7 +11492,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>17-02-2026 08:21:38</t>
+          <t>17-02-2026 08:17:21</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -11508,7 +11512,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26080522421800002767</t>
+          <t>26080522421710002766</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr"/>
@@ -11520,7 +11524,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -11532,12 +11536,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>344785</t>
+          <t>343350</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11547,17 +11551,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NAYELI</t>
+          <t>SOPHIA KENAI</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FARRERA</t>
+          <t>GARFIAS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VERDUGO</t>
+          <t xml:space="preserve"> SILVA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -11567,7 +11571,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6464000657</t>
+          <t>6462750693</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11578,17 +11582,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>13-09-1991</t>
+          <t>21-09-2007</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>NAYELLIFERRERA@GMAIL.COM</t>
+          <t>GRAFIAS12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>18-02-2026 11:03:42</t>
+          <t>12-02-2026 17:52:17</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11603,22 +11607,22 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>18-02-2026 11:05:18</t>
+          <t>12-02-2026 17:53:33</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -11635,36 +11639,36 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>26080522459270002847</t>
+          <t>26080522301000002563</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>344979</t>
+          <t>344601</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11674,17 +11678,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>INNEL CAROLINA</t>
+          <t xml:space="preserve">MARTIN DE JESUS </t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -11694,32 +11698,28 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6462234346</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462247390</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>11-09-1985</t>
+          <t>22-01-1992</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>INNELYA_11@HOTMAIL.COM</t>
+          <t>RAMIREZBRACO554@GMAIL.COM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>19-02-2026 06:53:45</t>
+          <t>17-02-2026 17:19:31</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11729,44 +11729,36 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>23-02-2026 18:33:46</t>
+          <t>19-02-2026 17:18:11</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>23-02-2026 18:31:37</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11774,7 +11766,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>26080522596180003109</t>
+          <t>26080522500880002947</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -11784,12 +11776,12 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>NAOMI LIZETH FLORES SANCHEZ</t>
+          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11806,12 +11798,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>345108</t>
+          <t>344877</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11821,17 +11813,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MARTHA IMELDA</t>
+          <t>JOSA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DRAGUSTINOVIS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -11841,32 +11833,28 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6461798580</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>3141475110</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>10-04-1967</t>
+          <t>15-11-2009</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>DRAGUSTINOVISMARTHA145@GMAIL.COM</t>
+          <t>JOSAGUTIERREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>19-02-2026 15:42:21</t>
+          <t>18-02-2026 16:52:22</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -11876,44 +11864,36 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>19-02-2026 15:50:59</t>
+          <t>18-02-2026 16:53:41</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>19-02-2026 15:50:24</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11921,36 +11901,36 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>26080522497630002935</t>
+          <t>26080522467540002872</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>344410</t>
+          <t>344785</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -11960,17 +11940,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>NAYELI</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>FARRERA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>VERDUGO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -11980,14 +11960,10 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6461298989</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6464000657</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -11995,64 +11971,56 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>24-05-1956</t>
+          <t>13-09-1991</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>PADILLARAQUEL45@GMAIL.COM</t>
+          <t>NAYELLIFERRERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>17-02-2026 08:14:06</t>
+          <t>18-02-2026 11:03:42</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>17-02-2026 08:18:21</t>
+          <t>18-02-2026 11:05:18</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>17-02-2026 08:17:21</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12060,36 +12028,36 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>26080522421710002766</t>
+          <t>26080522459270002847</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>344548</t>
+          <t>344979</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12099,17 +12067,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>INNEL CAROLINA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DUARTE </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -12119,28 +12087,32 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6644916747</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>6462234346</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>11-02-1991</t>
+          <t>11-09-1985</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>MANUELMORENA23@GMAIL.COM</t>
+          <t>INNELYA_11@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>17-02-2026 16:07:21</t>
+          <t>19-02-2026 06:53:45</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -12150,36 +12122,44 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>17-02-2026 16:08:29</t>
+          <t>23-02-2026 18:33:46</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:31:37</t>
+        </is>
+      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr"/>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W88" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12187,36 +12167,44 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>26080522432990002792</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
+          <t>26080522596180003109</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>NAOMI LIZETH FLORES SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>344091</t>
+          <t>345108</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>87273</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12226,17 +12214,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>MARTHA IMELDA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMBARENA </t>
+          <t>DRAGUSTINOVIS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELGADO </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -12246,7 +12234,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6461948652</t>
+          <t>6461798580</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -12261,52 +12249,52 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>06-09-2007</t>
+          <t>10-04-1967</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>VLARIALAMBARENA558@GMAIL.COM</t>
+          <t>DRAGUSTINOVISMARTHA145@GMAIL.COM</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>16-02-2026 14:19:45</t>
+          <t>19-02-2026 15:42:21</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>17-02-2026 13:22:02</t>
+          <t>19-02-2026 15:50:59</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>17-02-2026 13:21:30</t>
+          <t>19-02-2026 15:50:24</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -12316,7 +12304,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -12326,44 +12314,36 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>26080522427660002779</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
-        </is>
-      </c>
+          <t>26080522497630002935</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>344877</t>
+          <t>344091</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12373,17 +12353,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>JOSA</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">LAMBARENA </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">DELGADO </t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -12393,67 +12373,79 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>3141475110</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>6461948652</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>15-11-2009</t>
+          <t>06-09-2007</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>JOSAGUTIERREZ@GMAIL.COM</t>
+          <t>VLARIALAMBARENA558@GMAIL.COM</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>18-02-2026 16:52:22</t>
+          <t>16-02-2026 14:19:45</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>18-02-2026 16:53:41</t>
+          <t>17-02-2026 13:22:02</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>17-02-2026 13:21:30</t>
+        </is>
+      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W90" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12461,14 +12453,22 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>26080522467540002872</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
+          <t>26080522427660002779</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -12751,12 +12751,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>345421</t>
+          <t>346150</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>87586</t>
+          <t>88315</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12766,17 +12766,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t>ISAAC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>VERGARA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t>MUNGUIA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -12786,14 +12786,10 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>6613327166</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461076304</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -12801,64 +12797,56 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>28-08-2012</t>
+          <t>05-01-2005</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>PEDROVERGARA55@GMAIL.COM</t>
+          <t>KAAKMORAN3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>20-02-2026 20:44:02</t>
+          <t>24-02-2026 13:45:46</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>20-02-2026 20:50:55</t>
+          <t>24-02-2026 13:46:43</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>20-02-2026 20:50:08</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12866,14 +12854,14 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>26080522537020003019</t>
+          <t>26080522619450003175</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
@@ -12890,12 +12878,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>346150</t>
+          <t>346586</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>88315</t>
+          <t>88751</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12905,17 +12893,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ISAAC</t>
+          <t>ANA FERNANDA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MUNGUIA</t>
+          <t>ALDANA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -12925,28 +12913,28 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>6461076304</t>
+          <t>6462012063</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>05-01-2005</t>
+          <t>24-08-1986</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>KAAKMORAN3@GMAIL.COM</t>
+          <t>ORTIZALDANA45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>24-02-2026 13:45:46</t>
+          <t>25-02-2026 19:24:02</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -12971,18 +12959,18 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>24-02-2026 13:46:43</t>
+          <t>25-02-2026 19:24:58</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V94" t="inlineStr"/>
@@ -12993,7 +12981,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>26080522619450003175</t>
+          <t>26080522666000003305</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr"/>
@@ -13017,12 +13005,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>346586</t>
+          <t>345421</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>88751</t>
+          <t>87586</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -13032,17 +13020,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ANA FERNANDA</t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>VERGARA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ALDANA</t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -13052,67 +13040,79 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>6462012063</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>6613327166</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>24-08-1986</t>
+          <t>28-08-2012</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>ORTIZALDANA45@GMAIL.COM</t>
+          <t>PEDROVERGARA55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>25-02-2026 19:24:02</t>
+          <t>20-02-2026 20:44:02</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>25-02-2026 19:24:58</t>
+          <t>20-02-2026 20:50:55</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>20-02-2026 20:50:08</t>
+        </is>
+      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W95" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -13120,14 +13120,14 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>26080522666000003305</t>
+          <t>26080522537020003019</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
@@ -13271,12 +13271,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346142</t>
+          <t>278167</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>75668</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALVARO ALEJANDRO</t>
+          <t>YEIDD GERMAIONI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,28 +613,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3313728206</t>
+          <t>6161266824</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>04-07-1995</t>
+          <t>22-09-2006</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
+          <t>FIGUEROAYEIDD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>24-02-2026 12:50:39</t>
+          <t>10-02-2025 12:36:51</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 20:00:22</t>
+          <t>02-03-2026 16:43:54</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -681,14 +681,10 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26080522818500003629</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522802720003563</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -709,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>278167</t>
+          <t>329919</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>YEIDD GERMAIONI</t>
+          <t xml:space="preserve">MARTHA YOCELYN </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LORA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,7 +740,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6161266824</t>
+          <t>6461856343</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -755,17 +751,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22-09-2006</t>
+          <t>01-02-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FIGUEROAYEIDD@GMAIL.COM</t>
+          <t>YOCELYNRDGZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10-02-2025 12:36:51</t>
+          <t>22-12-2025 15:03:23</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -790,7 +786,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:43:54</t>
+          <t>02-03-2026 11:20:33</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26080522802720003563</t>
+          <t>26080522788960003528</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -836,12 +832,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>329919</t>
+          <t>286558</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>84057</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -851,17 +847,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA YOCELYN </t>
+          <t>OLGA ELENA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LORA</t>
+          <t>BUSTILLOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -871,10 +867,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6461856343</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6461163081</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -882,32 +882,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>01-02-2003</t>
+          <t>30-05-1988</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>YOCELYNRDGZ@GMAIL.COM</t>
+          <t>PSIC.OLGA.MORENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22-12-2025 15:03:23</t>
+          <t>05-04-2025 08:16:00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -917,21 +917,29 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:20:33</t>
+          <t>03-03-2026 17:58:13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:56:49</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -939,11 +947,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26080522788960003528</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26080522852900003716</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA TALAMANTES CARAVEO</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -963,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347612</t>
+          <t>346142</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>ALVARO ALEJANDRO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TAPIA </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -998,7 +1014,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6461977936</t>
+          <t>3313728206</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,22 +1025,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18-04-2006</t>
+          <t>04-07-1995</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
+          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:00:40</t>
+          <t>24-02-2026 12:50:39</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1034,17 +1050,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:01:59</t>
+          <t>02-03-2026 20:00:22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1055,7 +1071,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1066,14 +1082,18 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26080522796290003541</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26080522818500003629</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1090,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347853</t>
+          <t>347612</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1105,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PAUL ARMANDO</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABUNDIS </t>
+          <t xml:space="preserve"> TAPIA </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1125,7 +1145,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6461627211</t>
+          <t>6461977936</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,22 +1156,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-09-2009</t>
+          <t>18-04-2006</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PAULOLIVAREZ66@GMAIL.COM</t>
+          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:58</t>
+          <t>02-03-2026 15:00:40</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1161,17 +1181,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:08</t>
+          <t>02-03-2026 15:01:59</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1182,7 +1202,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1193,14 +1213,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26080522814300003609</t>
+          <t>26080522796290003541</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1217,12 +1237,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347744</t>
+          <t>347484</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89909</t>
+          <t>89649</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1232,17 +1252,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OMAR VALENTIN</t>
+          <t>JUANA ISABEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ADRIANO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1252,28 +1272,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6461506265</t>
+          <t>6461837342</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-08-1986</t>
+          <t>24-06-1967</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>OMARHHEREDIA90@GMAIL.COM</t>
+          <t>JISABELSANCHEZCHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:30:47</t>
+          <t>02-03-2026 10:23:03</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1298,18 +1318,18 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:07</t>
+          <t>03-03-2026 11:21:47</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1320,11 +1340,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26080522806860003575</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26080522837370003679</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>NOEH CORDOVA ensenada</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1344,12 +1372,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347749</t>
+          <t>347853</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89914</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1359,17 +1387,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMELA </t>
+          <t>PAUL ARMANDO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">ABUNDIS </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1379,28 +1407,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6461508603</t>
+          <t>6461627211</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-02-1986</t>
+          <t>14-09-2009</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PAMELASANCHEZ154@GMAIL.COM</t>
+          <t>PAULOLIVAREZ66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:59</t>
+          <t>02-03-2026 18:50:58</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1425,7 +1453,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:35:05</t>
+          <t>02-03-2026 18:52:08</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1436,7 +1464,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1447,7 +1475,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26080522807070003576</t>
+          <t>26080522814300003609</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1471,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347899</t>
+          <t>348177</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>90342</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1486,17 +1514,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA CRISTAL </t>
+          <t>FRANCISCO RUBEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JARQUIN</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1506,32 +1534,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9951043961</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462588234</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19-12-1998</t>
+          <t>31-05-1988</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
+          <t>RUBENCONTRERAS767@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 20:26:29</t>
+          <t>03-03-2026 17:28:07</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1541,44 +1565,36 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:23</t>
+          <t>03-03-2026 17:29:17</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:30:43</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1586,22 +1602,935 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26080522819690003636</t>
+          <t>26080522850990003711</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>348285</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90450</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MAYA DANIELA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ECHEVERRIA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6461922332</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>03-12-2006</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MAYAMORENO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:38:11</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:39:10</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26080522861280003745</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90172</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GALAAD SUJEY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MOJICA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6462563297</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOTAVENTO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>02-06-1992</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>GALAAD.MARTINEZM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:10:16</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:16:49</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:16:12</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26080522837280003678</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347899</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90064</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTHA CRISTAL </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTIAGO </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JARQUIN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>9951043961</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>19-12-1998</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:26:29</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:31:23</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:43</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26080522819690003636</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347744</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>89909</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OMAR VALENTIN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ADRIANO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HEREDIA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6461506265</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>03-08-1986</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OMARHHEREDIA90@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:30:47</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:33:07</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26080522806860003575</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347749</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>89914</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAMELA </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6461508603</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>28-02-1986</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PAMELASANCHEZ154@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:33:59</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:35:05</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26080522807070003576</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348162</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90327</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JOCELYN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ZEPEDA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6462707815</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>28-02-2009</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ZAPEDAJOCELYN55@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:19:25</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:21:34</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26080522850320003708</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348198</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90363</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JOSUE DANIEL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ESTUDILLO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CADENA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6462728748</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>28-10-2008</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>JOSUECADENA56@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:53:29</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26080522852480003714</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346142</t>
+          <t>226843</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALVARO ALEJANDRO</t>
+          <t>ISMAEL DAVID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>FRAGA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,10 +1014,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3313728206</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6461364250</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1025,32 +1029,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>04-07-1995</t>
+          <t>30-08-1986</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
+          <t>IDFRAGAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>24-02-2026 12:50:39</t>
+          <t>28-03-2024 13:02:51</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1060,21 +1064,29 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 20:00:22</t>
+          <t>05-03-2026 17:23:06</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:22:33</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1082,14 +1094,10 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26080522818500003629</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522923730003901</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1110,12 +1118,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347612</t>
+          <t>346142</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>ALVARO ALEJANDRO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TAPIA </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,7 +1153,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6461977936</t>
+          <t>3313728206</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,22 +1164,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18-04-2006</t>
+          <t>04-07-1995</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
+          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 15:00:40</t>
+          <t>24-02-2026 12:50:39</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1181,17 +1189,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 15:01:59</t>
+          <t>02-03-2026 20:00:22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1202,7 +1210,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1213,14 +1221,18 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26080522796290003541</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26080522818500003629</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1372,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347853</t>
+          <t>347612</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PAUL ARMANDO</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABUNDIS </t>
+          <t xml:space="preserve"> TAPIA </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,7 +1419,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6461627211</t>
+          <t>6461977936</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,22 +1430,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14-09-2009</t>
+          <t>18-04-2006</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PAULOLIVAREZ66@GMAIL.COM</t>
+          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:58</t>
+          <t>02-03-2026 15:00:40</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1443,17 +1455,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:08</t>
+          <t>02-03-2026 15:01:59</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1464,7 +1476,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1475,14 +1487,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26080522814300003609</t>
+          <t>26080522796290003541</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1499,12 +1511,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348177</t>
+          <t>348007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90342</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1514,17 +1526,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRANCISCO RUBEN</t>
+          <t>GALAAD SUJEY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>MOJICA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1534,53 +1546,57 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6462588234</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6462563297</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SOTAVENTO</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31-05-1988</t>
+          <t>02-06-1992</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>RUBENCONTRERAS767@GMAIL.COM</t>
+          <t>GALAAD.MARTINEZM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 17:28:07</t>
+          <t>03-03-2026 11:10:16</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 17:29:17</t>
+          <t>03-03-2026 11:16:49</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1588,13 +1604,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:16:12</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1602,14 +1626,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26080522850990003711</t>
+          <t>26080522837280003678</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1626,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348285</t>
+          <t>347383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90450</t>
+          <t>89548</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1641,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MAYA DANIELA</t>
+          <t>RODOLFO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ECHEVERRIA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>ARAIZA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1661,28 +1685,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6461922332</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6461324353</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BAHIA EL PLAYON</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>03-12-2006</t>
+          <t>27-08-1999</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MAYAMORENO@GMAIL.COM</t>
+          <t>RODOLFOMEZA42@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 20:38:11</t>
+          <t>02-03-2026 05:14:57</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1707,12 +1735,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 20:39:10</t>
+          <t>04-03-2026 05:10:02</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1729,7 +1757,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26080522861280003745</t>
+          <t>26080522864220003752</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1753,12 +1781,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348007</t>
+          <t>347767</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90172</t>
+          <t>89932</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1768,17 +1796,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GALAAD SUJEY</t>
+          <t>SABINA GUADALUPE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BASTIDAS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MOJICA</t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1788,14 +1816,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6462563297</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SOTAVENTO</t>
-        </is>
-      </c>
+          <t>6241347233</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1803,32 +1827,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>02-06-1992</t>
+          <t>28-01-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>GALAAD.MARTINEZM@GMAIL.COM</t>
+          <t>SABINACESEÑA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 11:10:16</t>
+          <t>02-03-2026 17:48:37</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1838,29 +1862,21 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 11:16:49</t>
+          <t>04-03-2026 13:17:36</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-03-2026 11:16:12</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1868,11 +1884,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26080522837280003678</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26080522881220003778</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1892,12 +1916,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347899</t>
+          <t>347744</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>89909</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1907,17 +1931,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA CRISTAL </t>
+          <t>OMAR VALENTIN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>ADRIANO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JARQUIN</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1927,57 +1951,53 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9951043961</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461506265</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19-12-1998</t>
+          <t>03-08-1986</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
+          <t>OMARHHEREDIA90@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:26:29</t>
+          <t>02-03-2026 17:30:47</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:23</t>
+          <t>02-03-2026 17:33:07</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1985,21 +2005,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:30:43</t>
-        </is>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2007,14 +2019,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26080522819690003636</t>
+          <t>26080522806860003575</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2031,12 +2043,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347744</t>
+          <t>347749</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89909</t>
+          <t>89914</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2046,17 +2058,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OMAR VALENTIN</t>
+          <t xml:space="preserve">PAMELA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ADRIANO</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2066,28 +2078,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6461506265</t>
+          <t>6461508603</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03-08-1986</t>
+          <t>28-02-1986</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OMARHHEREDIA90@GMAIL.COM</t>
+          <t>PAMELASANCHEZ154@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:30:47</t>
+          <t>02-03-2026 17:33:59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2112,7 +2124,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:07</t>
+          <t>02-03-2026 17:35:05</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2134,7 +2146,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26080522806860003575</t>
+          <t>26080522807070003576</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2158,12 +2170,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347749</t>
+          <t>347724</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89914</t>
+          <t>89889</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2173,12 +2185,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMELA </t>
+          <t>MORGAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>DE LA CERDA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2193,28 +2205,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6461508603</t>
+          <t>6462491023</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28-02-1986</t>
+          <t>22-01-2012</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PAMELASANCHEZ154@GMAIL.COM</t>
+          <t>MORGANDELACERDA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:59</t>
+          <t>02-03-2026 17:13:50</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2239,12 +2251,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 17:35:05</t>
+          <t>04-03-2026 18:34:50</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2261,11 +2273,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26080522807070003576</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26080522894790003821</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>549</t>
@@ -2273,24 +2293,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348162</t>
+          <t>347752</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90327</t>
+          <t>89917</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2300,17 +2320,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JOCELYN</t>
+          <t>ARIANA MARINA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>HIRALES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2320,7 +2340,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6462707815</t>
+          <t>6461184289</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2331,17 +2351,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>28-02-2009</t>
+          <t>01-03-1989</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ZAPEDAJOCELYN55@GMAIL.COM</t>
+          <t>ARIANAHILERA56@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 17:19:25</t>
+          <t>02-03-2026 17:36:39</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2366,18 +2386,18 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 17:21:34</t>
+          <t>05-03-2026 16:06:36</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2388,11 +2408,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26080522850320003708</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26080522920310003888</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>549</t>
@@ -2412,12 +2440,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348198</t>
+          <t>348473</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90363</t>
+          <t>90638</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2427,17 +2455,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JOSUE DANIEL</t>
+          <t xml:space="preserve">PEDRO ADRIAN </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ESTUDILLO</t>
+          <t xml:space="preserve">AYALA </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CADENA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2447,7 +2475,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6462728748</t>
+          <t>6462123059</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2458,22 +2486,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28-10-2008</t>
+          <t>23-10-1992</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JOSUECADENA56@GMAIL.COM</t>
+          <t>PEDROADRIAN523@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:53:29</t>
+          <t>04-03-2026 16:08:10</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2483,22 +2511,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:54:34</t>
+          <t>04-03-2026 16:10:23</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2515,14 +2543,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26080522852480003714</t>
+          <t>26080522886650003800</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2531,6 +2559,1864 @@
         </is>
       </c>
       <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348599</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90764</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BRYAN FABRICIO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ALEGRE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6863919612</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>21-12-2003</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>BRYANRUIZ65@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:20:01</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:26:28</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:25:57</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26080522899540003843</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>347899</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90064</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTHA CRISTAL </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTIAGO </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>JARQUIN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>9951043961</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>19-12-1998</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:26:29</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:31:23</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:43</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26080522819690003636</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348198</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90363</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JOSUE DANIEL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ESTUDILLO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CADENA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6462728748</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>28-10-2008</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>JOSUECADENA56@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:53:29</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26080522852480003714</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>347773</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>89938</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ANA JULISSA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MARQUEZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CESEÑA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6243581122</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>21-12-1994</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CESEÑAANA67@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:51:32</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>04-03-2026 13:18:37</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26080522881280003779</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>347908</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90073</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ARTURO JAVIER</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SALGADO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6241914236</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUANAVAL </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>19-04-1983</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CAN_IJO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:49:10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:24:25</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:23:56</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26080522875720003767</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348407</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90572</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CORAL IVETTE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CESEÑA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SEGOVIA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6461211789</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LOS PINOS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>18-08-1998</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CESENAIVETTE1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:47:36</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:56:37</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:55:48</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26080522880970003775</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Israel  Buzo Zamora</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348698</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90863</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERICKA NAYELY </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GALVAN </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6461018907</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>12-10-1997</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>RAMIREZGALVAN12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:11:34</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:19:10</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:18:19</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26080522916810003879</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348177</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90342</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FRANCISCO RUBEN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CONTRERAS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6462588234</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>31-05-1988</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>RUBENCONTRERAS767@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:28:07</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:29:17</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26080522850990003711</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348285</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90450</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MAYA DANIELA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ECHEVERRIA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6461922332</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>03-12-2006</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>MAYAMORENO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:38:11</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:39:10</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26080522861280003745</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348162</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90327</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>JOCELYN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ZEPEDA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6462707815</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>28-02-2009</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ZAPEDAJOCELYN55@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:19:25</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:21:34</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26080522850320003708</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>348163</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90328</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ARLETTE SHIOMARA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AMBRIZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6462716103</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>07-01-1992</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ORTIZSHIO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:19:48</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:26:21</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26080522923910003903</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348534</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90699</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MAYTE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARRA </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACOSTA </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6461030585</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15-11-2006</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PARRAACOSTA545@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:40:21</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:41:44</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26080522891580003816</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>347853</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90018</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PAUL ARMANDO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLIVARES </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABUNDIS </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6461627211</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>14-09-2009</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PAULOLIVAREZ66@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:50:58</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:52:08</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26080522814300003609</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348530</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90695</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>IVONNE PATRICIA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>REGALADO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ARCE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6198745369</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>29-12-1997</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>IVONNEARCE45@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:34:24</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:35:33</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26080522891200003815</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>278167</t>
+          <t>342902</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YEIDD GERMAIONI</t>
+          <t>ARIANA LIZETH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t xml:space="preserve">SEGOVIA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6161266824</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6461891033</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CALLE D 675</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -624,32 +628,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22-09-2006</t>
+          <t>05-11-2001</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FIGUEROAYEIDD@GMAIL.COM</t>
+          <t>ARIANA2MIRANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>10-02-2025 12:36:51</t>
+          <t>11-02-2026 08:17:09</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,21 +663,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 16:43:54</t>
+          <t>06-03-2026 10:46:49</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>06-03-2026 10:46:12</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,11 +693,19 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26080522802720003563</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26080522946660003949</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NAOMI LIZETH FLORES SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -705,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>329919</t>
+          <t>226843</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA YOCELYN </t>
+          <t>ISMAEL DAVID</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>FRAGA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LORA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,43 +760,47 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6461856343</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6461364250</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>01-02-2003</t>
+          <t>30-08-1986</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>YOCELYNRDGZ@GMAIL.COM</t>
+          <t>IDFRAGAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22-12-2025 15:03:23</t>
+          <t>28-03-2024 13:02:51</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -786,21 +810,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 11:20:33</t>
+          <t>05-03-2026 17:23:06</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:22:33</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -808,7 +840,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26080522788960003528</t>
+          <t>26080522923730003901</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -922,7 +954,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -979,12 +1011,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>226843</t>
+          <t>278167</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>75668</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +1026,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ISMAEL DAVID</t>
+          <t>YEIDD GERMAIONI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FRAGA</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,47 +1046,43 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6461364250</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6161266824</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30-08-1986</t>
+          <t>22-09-2006</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>IDFRAGAN@GMAIL.COM</t>
+          <t>FIGUEROAYEIDD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28-03-2024 13:02:51</t>
+          <t>10-02-2025 12:36:51</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1064,29 +1092,21 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>05-03-2026 17:23:06</t>
+          <t>02-03-2026 16:43:54</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>05-03-2026 17:22:33</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,7 +1114,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26080522923730003901</t>
+          <t>26080522802720003563</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1118,12 +1138,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346142</t>
+          <t>329919</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ALVARO ALEJANDRO</t>
+          <t xml:space="preserve">MARTHA YOCELYN </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>LORA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,28 +1173,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3313728206</t>
+          <t>6461856343</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>04-07-1995</t>
+          <t>01-02-2003</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
+          <t>YOCELYNRDGZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>24-02-2026 12:50:39</t>
+          <t>22-12-2025 15:03:23</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1199,12 +1219,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 20:00:22</t>
+          <t>02-03-2026 11:20:33</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1221,14 +1241,10 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26080522818500003629</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522788960003528</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1249,12 +1265,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347484</t>
+          <t>346142</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1280,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JUANA ISABEL</t>
+          <t>ALVARO ALEJANDRO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,28 +1300,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6461837342</t>
+          <t>3313728206</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-06-1967</t>
+          <t>04-07-1995</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JISABELSANCHEZCHAVEZ@GMAIL.COM</t>
+          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 10:23:03</t>
+          <t>24-02-2026 12:50:39</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1330,12 +1346,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 11:21:47</t>
+          <t>02-03-2026 20:00:22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1352,19 +1368,15 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26080522837370003679</t>
+          <t>26080522818500003629</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>NOEH CORDOVA ensenada</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1384,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347612</t>
+          <t>347383</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>89548</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>RODOLFO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TAPIA </t>
+          <t>ARAIZA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1419,10 +1431,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6461977936</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6461324353</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BAHIA EL PLAYON</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1430,22 +1446,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18-04-2006</t>
+          <t>27-08-1999</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
+          <t>RODOLFOMEZA42@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 15:00:40</t>
+          <t>02-03-2026 05:14:57</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1455,28 +1471,28 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 15:01:59</t>
+          <t>04-03-2026 05:10:02</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1487,14 +1503,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26080522796290003541</t>
+          <t>26080522864220003752</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1511,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348007</t>
+          <t>347484</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90172</t>
+          <t>89649</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1526,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GALAAD SUJEY</t>
+          <t>JUANA ISABEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MOJICA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1546,14 +1562,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6462563297</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>SOTAVENTO</t>
-        </is>
-      </c>
+          <t>6461837342</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1561,32 +1573,32 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>02-06-1992</t>
+          <t>24-06-1967</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GALAAD.MARTINEZM@GMAIL.COM</t>
+          <t>JISABELSANCHEZCHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 11:10:16</t>
+          <t>02-03-2026 10:23:03</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1596,29 +1608,21 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 11:16:49</t>
+          <t>03-03-2026 11:21:47</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>03-03-2026 11:16:12</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1626,11 +1630,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26080522837280003678</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26080522837370003679</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>NOEH CORDOVA ensenada</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1650,12 +1662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347383</t>
+          <t>347773</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89548</t>
+          <t>89938</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1665,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RODOLFO</t>
+          <t>ANA JULISSA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ARAIZA</t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1685,32 +1697,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6461324353</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>BAHIA EL PLAYON</t>
-        </is>
-      </c>
+          <t>6243581122</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27-08-1999</t>
+          <t>21-12-1994</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>RODOLFOMEZA42@GMAIL.COM</t>
+          <t>CESEÑAANA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 05:14:57</t>
+          <t>02-03-2026 17:51:32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1735,12 +1743,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 05:10:02</t>
+          <t>04-03-2026 13:18:37</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1757,11 +1765,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26080522864220003752</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26080522881280003779</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>549</t>
@@ -1781,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347767</t>
+          <t>347908</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89932</t>
+          <t>90073</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1796,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SABINA GUADALUPE</t>
+          <t>ARTURO JAVIER</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BASTIDAS</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CESEÑA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1816,67 +1832,79 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6241347233</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6241914236</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUANAVAL </t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-01-1995</t>
+          <t>19-04-1983</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SABINACESEÑA67@GMAIL.COM</t>
+          <t>CAN_IJO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:48:37</t>
+          <t>02-03-2026 20:49:10</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 13:17:36</t>
+          <t>04-03-2026 08:24:25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:23:56</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1884,44 +1912,40 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26080522881220003778</t>
+          <t>26080522875720003767</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347744</t>
+          <t>347724</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89909</t>
+          <t>89889</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1931,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OMAR VALENTIN</t>
+          <t>MORGAN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ADRIANO</t>
+          <t>DE LA CERDA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1951,7 +1975,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6461506265</t>
+          <t>6462491023</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1962,17 +1986,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>03-08-1986</t>
+          <t>22-01-2012</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OMARHHEREDIA90@GMAIL.COM</t>
+          <t>MORGANDELACERDA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 17:30:47</t>
+          <t>02-03-2026 17:13:50</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1997,12 +2021,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:07</t>
+          <t>04-03-2026 18:34:50</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2019,11 +2043,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26080522806860003575</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26080522894790003821</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2031,24 +2063,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347749</t>
+          <t>347752</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89914</t>
+          <t>89917</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2058,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMELA </t>
+          <t>ARIANA MARINA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>HIRALES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2078,7 +2110,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6461508603</t>
+          <t>6461184289</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2089,17 +2121,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28-02-1986</t>
+          <t>01-03-1989</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PAMELASANCHEZ154@GMAIL.COM</t>
+          <t>ARIANAHILERA56@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:59</t>
+          <t>02-03-2026 17:36:39</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2124,18 +2156,18 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:35:05</t>
+          <t>05-03-2026 16:06:36</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -2146,11 +2178,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26080522807070003576</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26080522920310003888</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2170,12 +2210,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347724</t>
+          <t>347767</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89889</t>
+          <t>89932</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2185,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MORGAN</t>
+          <t>SABINA GUADALUPE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DE LA CERDA</t>
+          <t>BASTIDAS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2205,28 +2245,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6462491023</t>
+          <t>6241347233</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22-01-2012</t>
+          <t>28-01-1995</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MORGANDELACERDA67@GMAIL.COM</t>
+          <t>SABINACESEÑA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 17:13:50</t>
+          <t>02-03-2026 17:48:37</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2251,18 +2291,18 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 18:34:50</t>
+          <t>04-03-2026 13:17:36</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2273,7 +2313,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26080522894790003821</t>
+          <t>26080522881220003778</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2293,24 +2333,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347752</t>
+          <t>347744</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89917</t>
+          <t>89909</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,17 +2360,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ARIANA MARINA</t>
+          <t>OMAR VALENTIN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>ADRIANO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HIRALES</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2340,28 +2380,28 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6461184289</t>
+          <t>6461506265</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>01-03-1989</t>
+          <t>03-08-1986</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ARIANAHILERA56@GMAIL.COM</t>
+          <t>OMARHHEREDIA90@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:36:39</t>
+          <t>02-03-2026 17:30:47</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2386,18 +2426,18 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>05-03-2026 16:06:36</t>
+          <t>02-03-2026 17:33:07</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2408,19 +2448,11 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26080522920310003888</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>26080522806860003575</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>549</t>
@@ -2440,12 +2472,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348473</t>
+          <t>347749</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90638</t>
+          <t>89914</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2455,17 +2487,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO ADRIAN </t>
+          <t xml:space="preserve">PAMELA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYALA </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2475,33 +2507,33 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6462123059</t>
+          <t>6461508603</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>23-10-1992</t>
+          <t>28-02-1986</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PEDROADRIAN523@GMAIL.COM</t>
+          <t>PAMELASANCHEZ154@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>04-03-2026 16:08:10</t>
+          <t>02-03-2026 17:33:59</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2511,22 +2543,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-03-2026 16:10:23</t>
+          <t>02-03-2026 17:35:05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2543,14 +2575,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26080522886650003800</t>
+          <t>26080522807070003576</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2567,12 +2599,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348599</t>
+          <t>347853</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90764</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2582,17 +2614,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BRYAN FABRICIO</t>
+          <t>PAUL ARMANDO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ALEGRE</t>
+          <t xml:space="preserve">ABUNDIS </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2602,14 +2634,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6863919612</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461627211</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2617,32 +2645,32 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21-12-2003</t>
+          <t>14-09-2009</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BRYANRUIZ65@GMAIL.COM</t>
+          <t>PAULOLIVAREZ66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-03-2026 20:20:01</t>
+          <t>02-03-2026 18:50:58</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2652,29 +2680,21 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-03-2026 20:26:28</t>
+          <t>02-03-2026 18:52:08</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>04-03-2026 20:25:57</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2682,7 +2702,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26080522899540003843</t>
+          <t>26080522814300003609</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2706,12 +2726,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347899</t>
+          <t>348177</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>90342</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2721,17 +2741,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA CRISTAL </t>
+          <t>FRANCISCO RUBEN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JARQUIN</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2741,32 +2761,28 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9951043961</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462588234</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19-12-1998</t>
+          <t>31-05-1988</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
+          <t>RUBENCONTRERAS767@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 20:26:29</t>
+          <t>03-03-2026 17:28:07</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2776,22 +2792,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:23</t>
+          <t>03-03-2026 17:29:17</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2799,21 +2815,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:30:43</t>
-        </is>
-      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2821,14 +2829,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26080522819690003636</t>
+          <t>26080522850990003711</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2845,12 +2853,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348198</t>
+          <t>347899</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90363</t>
+          <t>90064</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2860,17 +2868,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JOSUE DANIEL</t>
+          <t xml:space="preserve">MARTHA CRISTAL </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ESTUDILLO</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CADENA</t>
+          <t>JARQUIN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2880,67 +2888,79 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6462728748</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>9951043961</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>28-10-2008</t>
+          <t>19-12-1998</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JOSUECADENA56@GMAIL.COM</t>
+          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:53:29</t>
+          <t>02-03-2026 20:26:29</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:54:34</t>
+          <t>02-03-2026 20:31:23</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:43</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2948,14 +2968,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26080522852480003714</t>
+          <t>26080522819690003636</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2972,12 +2992,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347773</t>
+          <t>348530</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89938</t>
+          <t>90695</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2987,17 +3007,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANA JULISSA</t>
+          <t>IVONNE PATRICIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>REGALADO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CESEÑA</t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3007,7 +3027,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6243581122</t>
+          <t>6198745369</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3018,22 +3038,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21-12-1994</t>
+          <t>29-12-1997</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CESEÑAANA67@GMAIL.COM</t>
+          <t>IVONNEARCE45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 17:51:32</t>
+          <t>04-03-2026 17:34:24</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3043,22 +3063,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-03-2026 13:18:37</t>
+          <t>04-03-2026 17:35:33</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -3075,22 +3095,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26080522881280003779</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>26080522891200003815</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3107,12 +3119,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347908</t>
+          <t>348285</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90073</t>
+          <t>90450</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3122,17 +3134,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ARTURO JAVIER</t>
+          <t>MAYA DANIELA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>ECHEVERRIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3142,79 +3154,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6241914236</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AGUANAVAL </t>
-        </is>
-      </c>
+          <t>6461922332</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19-04-1983</t>
+          <t>03-12-2006</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CAN_IJO@HOTMAIL.COM</t>
+          <t>MAYAMORENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 20:49:10</t>
+          <t>03-03-2026 20:38:11</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-03-2026 08:24:25</t>
+          <t>03-03-2026 20:39:10</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>04-03-2026 08:23:56</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3222,18 +3222,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26080522875720003767</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26080522861280003745</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3250,12 +3246,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348407</t>
+          <t>348163</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90572</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3265,17 +3261,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CORAL IVETTE</t>
+          <t>ARLETTE SHIOMARA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CESEÑA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3285,14 +3281,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6461211789</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>LOS PINOS</t>
-        </is>
-      </c>
+          <t>6462716103</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3300,32 +3292,32 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18-08-1998</t>
+          <t>07-01-1992</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CESENAIVETTE1@GMAIL.COM</t>
+          <t>ORTIZSHIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-03-2026 12:47:36</t>
+          <t>03-03-2026 17:19:48</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3335,7 +3327,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-03-2026 12:56:37</t>
+          <t>05-03-2026 17:26:21</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3343,21 +3335,13 @@
           <t>04-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>04-03-2026 12:55:48</t>
-        </is>
-      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3365,11 +3349,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26080522880970003775</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26080522923910003903</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>549</t>
@@ -3377,7 +3369,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3389,12 +3381,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348698</t>
+          <t>348198</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90863</t>
+          <t>90363</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3404,17 +3396,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERICKA NAYELY </t>
+          <t>JOSUE DANIEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>ESTUDILLO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>CADENA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3424,47 +3416,43 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6461018907</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6462728748</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-10-1997</t>
+          <t>28-10-2008</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>RAMIREZGALVAN12@GMAIL.COM</t>
+          <t>JOSUECADENA56@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>05-03-2026 14:11:34</t>
+          <t>03-03-2026 17:53:29</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3474,29 +3462,21 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-03-2026 14:19:10</t>
+          <t>03-03-2026 17:54:34</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>05-03-2026 14:18:19</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3504,7 +3484,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26080522916810003879</t>
+          <t>26080522852480003714</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3528,12 +3508,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348177</t>
+          <t>348407</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90342</t>
+          <t>90572</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3543,17 +3523,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FRANCISCO RUBEN</t>
+          <t>CORAL IVETTE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3563,53 +3543,57 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6462588234</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6461211789</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LOS PINOS</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31-05-1988</t>
+          <t>18-08-1998</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>RUBENCONTRERAS767@GMAIL.COM</t>
+          <t>CESENAIVETTE1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-03-2026 17:28:07</t>
+          <t>04-03-2026 12:47:36</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-03-2026 17:29:17</t>
+          <t>04-03-2026 12:56:37</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3617,13 +3601,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:55:48</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3631,36 +3623,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26080522850990003711</t>
+          <t>26080522880970003775</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348285</t>
+          <t>348162</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90450</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3670,17 +3662,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MAYA DANIELA</t>
+          <t>JOCELYN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECHEVERRIA</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3690,7 +3682,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6461922332</t>
+          <t>6462707815</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3701,17 +3693,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03-12-2006</t>
+          <t>28-02-2009</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MAYAMORENO@GMAIL.COM</t>
+          <t>ZAPEDAJOCELYN55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-03-2026 20:38:11</t>
+          <t>03-03-2026 17:19:25</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3736,18 +3728,18 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 20:39:10</t>
+          <t>03-03-2026 17:21:34</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3758,7 +3750,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26080522861280003745</t>
+          <t>26080522850320003708</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3782,12 +3774,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348162</t>
+          <t>347612</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90327</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3797,17 +3789,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOCELYN</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve"> TAPIA </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3817,33 +3809,33 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6462707815</t>
+          <t>6461977936</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28-02-2009</t>
+          <t>18-04-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ZAPEDAJOCELYN55@GMAIL.COM</t>
+          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 17:19:25</t>
+          <t>02-03-2026 15:00:40</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3853,22 +3845,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-03-2026 17:21:34</t>
+          <t>02-03-2026 15:01:59</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3885,14 +3877,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26080522850320003708</t>
+          <t>26080522796290003541</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3909,12 +3901,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>348163</t>
+          <t>348007</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3924,17 +3916,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ARLETTE SHIOMARA</t>
+          <t>GALAAD SUJEY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMBRIZ</t>
+          <t>MOJICA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3944,10 +3936,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6462716103</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6462563297</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SOTAVENTO</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3955,32 +3951,32 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>07-01-1992</t>
+          <t>02-06-1992</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ORTIZSHIO@GMAIL.COM</t>
+          <t>GALAAD.MARTINEZM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>03-03-2026 17:19:48</t>
+          <t>03-03-2026 11:10:16</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3990,21 +3986,29 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>05-03-2026 17:26:21</t>
+          <t>03-03-2026 11:16:49</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:16:12</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4012,19 +4016,11 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26080522923910003903</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>26080522837280003678</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>549</t>
@@ -4044,12 +4040,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348534</t>
+          <t>349154</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>91319</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4059,17 +4055,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MAYTE</t>
+          <t xml:space="preserve">MARGARITA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACOSTA </t>
+          <t xml:space="preserve">VALLEJO </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4079,10 +4075,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6461030585</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6461141936</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4090,56 +4090,64 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15-11-2006</t>
+          <t>06-12-1980</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PARRAACOSTA545@GMAIL.COM</t>
+          <t>MARGARITAGUZMA4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>04-03-2026 17:40:21</t>
+          <t>07-03-2026 13:10:51</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04-03-2026 17:41:44</t>
+          <t>07-03-2026 13:16:39</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:15:54</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4147,14 +4155,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26080522891580003816</t>
+          <t>26080522975620004027</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4171,12 +4179,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347853</t>
+          <t>348534</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>90699</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4186,17 +4194,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PAUL ARMANDO</t>
+          <t>MAYTE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABUNDIS </t>
+          <t xml:space="preserve">ACOSTA </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4206,28 +4214,28 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6461627211</t>
+          <t>6461030585</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>14-09-2009</t>
+          <t>15-11-2006</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PAULOLIVAREZ66@GMAIL.COM</t>
+          <t>PARRAACOSTA545@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:58</t>
+          <t>04-03-2026 17:40:21</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4252,18 +4260,18 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:08</t>
+          <t>04-03-2026 17:41:44</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -4274,7 +4282,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26080522814300003609</t>
+          <t>26080522891580003816</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4298,12 +4306,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348530</t>
+          <t>348698</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90695</t>
+          <t>90863</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4313,17 +4321,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IVONNE PATRICIA</t>
+          <t xml:space="preserve">ERICKA NAYELY </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>REGALADO</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4333,10 +4341,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6198745369</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6461018907</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4344,42 +4356,42 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>29-12-1997</t>
+          <t>12-10-1997</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>IVONNEARCE45@GMAIL.COM</t>
+          <t>RAMIREZGALVAN12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>04-03-2026 17:34:24</t>
+          <t>05-03-2026 14:11:34</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>04-03-2026 17:35:33</t>
+          <t>05-03-2026 14:19:10</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4387,13 +4399,21 @@
           <t>04-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:18:19</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4401,22 +4421,288 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26080522891200003815</t>
+          <t>26080522916810003879</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348473</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90638</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEDRO ADRIAN </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AYALA </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6462123059</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23-10-1992</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PEDROADRIAN523@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:08:10</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:10:23</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26080522886650003800</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>348599</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>90764</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BRYAN FABRICIO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ALEGRE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6863919612</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>21-12-2003</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>BRYANRUIZ65@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:20:01</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:26:28</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:25:57</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26080522899540003843</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__MISION ENS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>342902</t>
+          <t>278167</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>75668</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ARIANA LIZETH</t>
+          <t>YEIDD GERMAIONI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGOVIA </t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6461891033</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>CALLE D 675</t>
-        </is>
-      </c>
+          <t>6161266824</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -628,32 +624,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>05-11-2001</t>
+          <t>22-09-2006</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ARIANA2MIRANDA@GMAIL.COM</t>
+          <t>FIGUEROAYEIDD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>11-02-2026 08:17:09</t>
+          <t>10-02-2025 12:36:51</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,29 +659,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06-03-2026 10:46:49</t>
+          <t>02-03-2026 16:43:54</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>06-03-2026 10:46:12</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,19 +681,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26080522946660003949</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>NAOMI LIZETH FLORES SANCHEZ</t>
-        </is>
-      </c>
+          <t>26080522802720003563</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -725,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>226843</t>
+          <t>329919</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ISMAEL DAVID</t>
+          <t xml:space="preserve">MARTHA YOCELYN </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FRAGA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LORA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,47 +740,43 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6461364250</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461856343</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30-08-1986</t>
+          <t>01-02-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IDFRAGAN@GMAIL.COM</t>
+          <t>YOCELYNRDGZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-03-2024 13:02:51</t>
+          <t>22-12-2025 15:03:23</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -810,29 +786,21 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>05-03-2026 17:23:06</t>
+          <t>02-03-2026 11:20:33</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>05-03-2026 17:22:33</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -840,7 +808,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26080522923730003901</t>
+          <t>26080522788960003528</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -1011,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>278167</t>
+          <t>226843</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1026,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YEIDD GERMAIONI</t>
+          <t>ISMAEL DAVID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>FRAGA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1046,43 +1014,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6161266824</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6461364250</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22-09-2006</t>
+          <t>30-08-1986</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FIGUEROAYEIDD@GMAIL.COM</t>
+          <t>IDFRAGAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10-02-2025 12:36:51</t>
+          <t>28-03-2024 13:02:51</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1092,21 +1064,29 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:43:54</t>
+          <t>05-03-2026 17:23:06</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:22:33</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1114,7 +1094,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26080522802720003563</t>
+          <t>26080522923730003901</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1138,12 +1118,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>329919</t>
+          <t>346142</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA YOCELYN </t>
+          <t>ALVARO ALEJANDRO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LORA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,28 +1153,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6461856343</t>
+          <t>3313728206</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>01-02-2003</t>
+          <t>04-07-1995</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>YOCELYNRDGZ@GMAIL.COM</t>
+          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22-12-2025 15:03:23</t>
+          <t>24-02-2026 12:50:39</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1219,7 +1199,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 11:20:33</t>
+          <t>02-03-2026 20:00:22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1241,10 +1221,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26080522788960003528</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26080522818500003629</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1265,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>346142</t>
+          <t>342902</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALVARO ALEJANDRO</t>
+          <t>ARIANA LIZETH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t xml:space="preserve">SEGOVIA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,43 +1284,47 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3313728206</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6461891033</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CALLE D 675</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>04-07-1995</t>
+          <t>05-11-2001</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ALVARORIOSCASTRO@GMAIL.COM</t>
+          <t>ARIANA2MIRANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>24-02-2026 12:50:39</t>
+          <t>11-02-2026 08:17:09</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1346,21 +1334,29 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 20:00:22</t>
+          <t>06-03-2026 10:46:49</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>06-03-2026 10:46:12</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1368,15 +1364,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26080522818500003629</t>
+          <t>26080522946660003949</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>NAOMI LIZETH FLORES SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1527,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347484</t>
+          <t>347488</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>89653</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JUANA ISABEL</t>
+          <t>PERLA LIZBETH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ENCISO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>LANDA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,10 +1562,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6461837342</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6463874007</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21 DE MARZO </t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1573,56 +1577,64 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24-06-1967</t>
+          <t>14-02-2003</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JISABELSANCHEZCHAVEZ@GMAIL.COM</t>
+          <t>ENCISO.PERLA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 10:23:03</t>
+          <t>02-03-2026 10:30:51</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 11:21:47</t>
+          <t>09-03-2026 07:24:14</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:23:33</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1630,22 +1642,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26080522837370003679</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>NOEH CORDOVA ensenada</t>
-        </is>
-      </c>
+          <t>26080522998920004063</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1662,12 +1666,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347773</t>
+          <t>346823</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89938</t>
+          <t>88988</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ANA JULISSA</t>
+          <t>AIDE BRISEIDA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CESEÑA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,10 +1701,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6243581122</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6461611449</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1708,32 +1716,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21-12-1994</t>
+          <t>05-07-1982</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CESEÑAANA67@GMAIL.COM</t>
+          <t>AIDERAMIRES89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:51:32</t>
+          <t>26-02-2026 19:20:19</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1743,21 +1751,29 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 13:18:37</t>
+          <t>12-03-2026 19:16:17</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:15:40</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1765,7 +1781,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26080522881280003779</t>
+          <t>26080523134080004449</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1797,12 +1813,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347908</t>
+          <t>347484</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90073</t>
+          <t>89649</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ARTURO JAVIER</t>
+          <t>JUANA ISABEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,79 +1848,67 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6241914236</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AGUANAVAL </t>
-        </is>
-      </c>
+          <t>6461837342</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19-04-1983</t>
+          <t>24-06-1967</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CAN_IJO@HOTMAIL.COM</t>
+          <t>JISABELSANCHEZCHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 20:49:10</t>
+          <t>02-03-2026 10:23:03</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 08:24:25</t>
+          <t>03-03-2026 11:21:47</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>04-03-2026 08:23:56</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1912,40 +1916,44 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26080522875720003767</t>
+          <t>26080522837370003679</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>NOEH CORDOVA ensenada</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Christian Eduardo Hermosillo Diaz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347724</t>
+          <t>347489</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89889</t>
+          <t>89654</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MORGAN</t>
+          <t>BEATRIZ ANDREA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DE LA CERDA</t>
+          <t>ENCISO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LANDA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,67 +1983,79 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6462491023</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6865898112</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20 DE NOVIEMBRE 275</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22-01-2012</t>
+          <t>15-05-1998</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MORGANDELACERDA67@GMAIL.COM</t>
+          <t>6865898112A@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 17:13:50</t>
+          <t>02-03-2026 10:33:46</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 18:34:50</t>
+          <t>09-03-2026 07:28:57</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:28:21</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2043,44 +2063,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26080522894790003821</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>26080522999050004064</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347752</t>
+          <t>346782</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89917</t>
+          <t>88947</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2102,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ARIANA MARINA</t>
+          <t>CESA AGUSTIN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MUNGUIA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HIRALES</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,28 +2122,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6461184289</t>
+          <t>6462872776</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>01-03-1989</t>
+          <t>14-12-2011</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ARIANAHILERA56@GMAIL.COM</t>
+          <t>BARBARA70384@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:36:39</t>
+          <t>26-02-2026 17:43:09</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2156,18 +2168,18 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05-03-2026 16:06:36</t>
+          <t>10-03-2026 13:29:28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -2178,7 +2190,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26080522920310003888</t>
+          <t>26080523051270004218</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2210,12 +2222,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347767</t>
+          <t>347773</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89932</t>
+          <t>89938</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2225,12 +2237,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SABINA GUADALUPE</t>
+          <t>ANA JULISSA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BASTIDAS</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2245,7 +2257,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6241347233</t>
+          <t>6243581122</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2256,17 +2268,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28-01-1995</t>
+          <t>21-12-1994</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SABINACESEÑA67@GMAIL.COM</t>
+          <t>CESEÑAANA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 17:48:37</t>
+          <t>02-03-2026 17:51:32</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2291,7 +2303,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 13:17:36</t>
+          <t>04-03-2026 13:18:37</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2313,7 +2325,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26080522881220003778</t>
+          <t>26080522881280003779</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2345,12 +2357,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347744</t>
+          <t>347853</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89909</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2360,17 +2372,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OMAR VALENTIN</t>
+          <t>PAUL ARMANDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ADRIANO</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t xml:space="preserve">ABUNDIS </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2380,7 +2392,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6461506265</t>
+          <t>6461627211</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2391,17 +2403,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>03-08-1986</t>
+          <t>14-09-2009</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>OMARHHEREDIA90@GMAIL.COM</t>
+          <t>PAULOLIVAREZ66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:30:47</t>
+          <t>02-03-2026 18:50:58</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2426,7 +2438,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:07</t>
+          <t>02-03-2026 18:52:08</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2437,7 +2449,7 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2448,7 +2460,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26080522806860003575</t>
+          <t>26080522814300003609</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2460,24 +2472,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347749</t>
+          <t>347767</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89914</t>
+          <t>89932</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2499,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMELA </t>
+          <t>SABINA GUADALUPE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>BASTIDAS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,7 +2519,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6461508603</t>
+          <t>6241347233</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2518,17 +2530,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28-02-1986</t>
+          <t>28-01-1995</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PAMELASANCHEZ154@GMAIL.COM</t>
+          <t>SABINACESEÑA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:33:59</t>
+          <t>02-03-2026 17:48:37</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2553,18 +2565,18 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:35:05</t>
+          <t>04-03-2026 13:17:36</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2575,11 +2587,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26080522807070003576</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26080522881220003778</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>549</t>
@@ -2599,12 +2619,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347853</t>
+          <t>347899</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>90064</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2614,17 +2634,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PAUL ARMANDO</t>
+          <t xml:space="preserve">MARTHA CRISTAL </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABUNDIS </t>
+          <t>JARQUIN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2634,53 +2654,57 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6461627211</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>9951043961</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14-09-2009</t>
+          <t>19-12-1998</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PAULOLIVAREZ66@GMAIL.COM</t>
+          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:58</t>
+          <t>02-03-2026 20:26:29</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:08</t>
+          <t>02-03-2026 20:31:23</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2688,13 +2712,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:43</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2702,14 +2734,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26080522814300003609</t>
+          <t>26080522819690003636</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2726,12 +2758,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348177</t>
+          <t>347744</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90342</t>
+          <t>89909</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2741,17 +2773,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FRANCISCO RUBEN</t>
+          <t>OMAR VALENTIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>ADRIANO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2761,7 +2793,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6462588234</t>
+          <t>6461506265</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2772,22 +2804,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31-05-1988</t>
+          <t>03-08-1986</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>RUBENCONTRERAS767@GMAIL.COM</t>
+          <t>OMARHHEREDIA90@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 17:28:07</t>
+          <t>02-03-2026 17:30:47</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2797,22 +2829,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 17:29:17</t>
+          <t>02-03-2026 17:33:07</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2829,14 +2861,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26080522850990003711</t>
+          <t>26080522806860003575</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2853,12 +2885,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347899</t>
+          <t>347749</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>89914</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2868,17 +2900,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA CRISTAL </t>
+          <t xml:space="preserve">PAMELA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JARQUIN</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2888,14 +2920,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9951043961</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461508603</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2903,42 +2931,42 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19-12-1998</t>
+          <t>28-02-1986</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SATIAGOJARQUIN66@GMAIL.COM</t>
+          <t>PAMELASANCHEZ154@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 20:26:29</t>
+          <t>02-03-2026 17:33:59</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:23</t>
+          <t>02-03-2026 17:35:05</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2946,21 +2974,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:30:43</t>
-        </is>
-      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2968,14 +2988,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26080522819690003636</t>
+          <t>26080522807070003576</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2992,12 +3012,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348530</t>
+          <t>347724</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90695</t>
+          <t>89889</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3007,17 +3027,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IVONNE PATRICIA</t>
+          <t>MORGAN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>REGALADO</t>
+          <t>DE LA CERDA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3027,33 +3047,33 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6198745369</t>
+          <t>6462491023</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>29-12-1997</t>
+          <t>22-01-2012</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IVONNEARCE45@GMAIL.COM</t>
+          <t>MORGANDELACERDA67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-03-2026 17:34:24</t>
+          <t>02-03-2026 17:13:50</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3063,17 +3083,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-03-2026 17:35:33</t>
+          <t>04-03-2026 18:34:50</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3084,7 +3104,7 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -3095,36 +3115,44 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26080522891200003815</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26080522894790003821</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348285</t>
+          <t>347752</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90450</t>
+          <t>89917</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3134,17 +3162,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MAYA DANIELA</t>
+          <t>ARIANA MARINA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ECHEVERRIA</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>HIRALES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3154,7 +3182,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6461922332</t>
+          <t>6461184289</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3165,17 +3193,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>03-12-2006</t>
+          <t>01-03-1989</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MAYAMORENO@GMAIL.COM</t>
+          <t>ARIANAHILERA56@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 20:38:11</t>
+          <t>02-03-2026 17:36:39</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3200,12 +3228,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 20:39:10</t>
+          <t>05-03-2026 16:06:36</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3222,11 +3250,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26080522861280003745</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26080522920310003888</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>549</t>
@@ -3234,24 +3270,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348163</t>
+          <t>347612</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3261,17 +3297,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ARLETTE SHIOMARA</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AMBRIZ</t>
+          <t xml:space="preserve"> TAPIA </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3281,33 +3317,33 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6462716103</t>
+          <t>6461977936</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>07-01-1992</t>
+          <t>18-04-2006</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ORTIZSHIO@GMAIL.COM</t>
+          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 17:19:48</t>
+          <t>02-03-2026 15:00:40</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3317,28 +3353,28 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>05-03-2026 17:26:21</t>
+          <t>02-03-2026 15:01:59</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -3349,44 +3385,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26080522923910003903</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
-        </is>
-      </c>
+          <t>26080522796290003541</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>David Alejandro  Vasquez Felix</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348198</t>
+          <t>347908</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90363</t>
+          <t>90073</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3396,17 +3424,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOSUE DANIEL</t>
+          <t>ARTURO JAVIER</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ESTUDILLO</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CADENA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3416,10 +3444,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6462728748</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6241914236</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUANAVAL </t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3427,56 +3459,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-10-2008</t>
+          <t>19-04-1983</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JOSUECADENA56@GMAIL.COM</t>
+          <t>CAN_IJO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 17:53:29</t>
+          <t>02-03-2026 20:49:10</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-03-2026 17:54:34</t>
+          <t>04-03-2026 08:24:25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:23:56</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3484,36 +3524,40 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26080522852480003714</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
+          <t>26080522875720003767</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Eduardo Hermosillo Diaz</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348407</t>
+          <t>348163</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90572</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3523,17 +3567,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CORAL IVETTE</t>
+          <t>ARLETTE SHIOMARA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CESEÑA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3543,14 +3587,10 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6461211789</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>LOS PINOS</t>
-        </is>
-      </c>
+          <t>6462716103</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3558,32 +3598,32 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18-08-1998</t>
+          <t>07-01-1992</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CESENAIVETTE1@GMAIL.COM</t>
+          <t>ORTIZSHIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-03-2026 12:47:36</t>
+          <t>03-03-2026 17:19:48</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3593,29 +3633,21 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-03-2026 12:56:37</t>
+          <t>05-03-2026 17:26:21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>04-03-2026 12:55:48</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3623,11 +3655,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26080522880970003775</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26080522923910003903</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>DANIA XIMENA  PERALTA PIÑUELAS</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>549</t>
@@ -3635,7 +3675,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Israel  Buzo Zamora</t>
+          <t>David Alejandro  Vasquez Felix</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3647,12 +3687,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348162</t>
+          <t>348198</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90327</t>
+          <t>90363</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3662,17 +3702,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JOCELYN</t>
+          <t>JOSUE DANIEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>ESTUDILLO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CADENA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3682,28 +3722,28 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6462707815</t>
+          <t>6462728748</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>28-02-2009</t>
+          <t>28-10-2008</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ZAPEDAJOCELYN55@GMAIL.COM</t>
+          <t>JOSUECADENA56@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-03-2026 17:19:25</t>
+          <t>03-03-2026 17:53:29</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3728,7 +3768,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 17:21:34</t>
+          <t>03-03-2026 17:54:34</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3750,7 +3790,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26080522850320003708</t>
+          <t>26080522852480003714</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3774,12 +3814,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347612</t>
+          <t>348530</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>90695</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3789,17 +3829,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>IVONNE PATRICIA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>REGALADO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TAPIA </t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3809,28 +3849,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6461977936</t>
+          <t>6198745369</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18-04-2006</t>
+          <t>29-12-1997</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CAMACHOALEJANDRO54@GMAIL.COM</t>
+          <t>IVONNEARCE45@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 15:00:40</t>
+          <t>04-03-2026 17:34:24</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3855,18 +3895,18 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 15:01:59</t>
+          <t>04-03-2026 17:35:33</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3877,7 +3917,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26080522796290003541</t>
+          <t>26080522891200003815</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3901,12 +3941,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>348007</t>
+          <t>348162</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90172</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3916,19 +3956,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GALAAD SUJEY</t>
+          <t>JOCELYN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>ZEPEDA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>MARTINEZ</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>MOJICA</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>52</t>
@@ -3936,14 +3976,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6462563297</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>SOTAVENTO</t>
-        </is>
-      </c>
+          <t>6462707815</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3951,32 +3987,32 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>02-06-1992</t>
+          <t>28-02-2009</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>GALAAD.MARTINEZM@GMAIL.COM</t>
+          <t>ZAPEDAJOCELYN55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>03-03-2026 11:10:16</t>
+          <t>03-03-2026 17:19:25</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3986,7 +4022,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-03-2026 11:16:49</t>
+          <t>03-03-2026 17:21:34</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3994,21 +4030,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>03-03-2026 11:16:12</t>
-        </is>
-      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4016,7 +4044,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26080522837280003678</t>
+          <t>26080522850320003708</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4040,12 +4068,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>349154</t>
+          <t>348407</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>91319</t>
+          <t>90572</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4055,17 +4083,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARGARITA </t>
+          <t>CORAL IVETTE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t>CESEÑA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALLEJO </t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4075,12 +4103,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6461141936</t>
+          <t>6461211789</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LOS PINOS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4090,52 +4118,52 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>06-12-1980</t>
+          <t>18-08-1998</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MARGARITAGUZMA4@GMAIL.COM</t>
+          <t>CESENAIVETTE1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>07-03-2026 13:10:51</t>
+          <t>04-03-2026 12:47:36</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>07-03-2026 13:16:39</t>
+          <t>04-03-2026 12:56:37</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>07-03-2026 13:15:54</t>
+          <t>04-03-2026 12:55:48</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4145,7 +4173,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4155,36 +4183,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26080522975620004027</t>
+          <t>26080522880970003775</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Israel  Buzo Zamora</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>348534</t>
+          <t>348007</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4194,17 +4222,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MAYTE</t>
+          <t>GALAAD SUJEY</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACOSTA </t>
+          <t>MOJICA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4214,10 +4242,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6461030585</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6462563297</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SOTAVENTO</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4225,32 +4257,32 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>15-11-2006</t>
+          <t>02-06-1992</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PARRAACOSTA545@GMAIL.COM</t>
+          <t>GALAAD.MARTINEZM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>04-03-2026 17:40:21</t>
+          <t>03-03-2026 11:10:16</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4260,21 +4292,29 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>04-03-2026 17:41:44</t>
+          <t>03-03-2026 11:16:49</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:16:12</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4282,7 +4322,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26080522891580003816</t>
+          <t>26080522837280003678</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4294,24 +4334,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aaron Felipe Aguilar Grave</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348698</t>
+          <t>348534</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90863</t>
+          <t>90699</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4321,17 +4361,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERICKA NAYELY </t>
+          <t>MAYTE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t xml:space="preserve">ACOSTA </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4341,14 +4381,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6461018907</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461030585</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4356,32 +4392,32 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>12-10-1997</t>
+          <t>15-11-2006</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>RAMIREZGALVAN12@GMAIL.COM</t>
+          <t>PARRAACOSTA545@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>05-03-2026 14:11:34</t>
+          <t>04-03-2026 17:40:21</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4391,29 +4427,21 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>05-03-2026 14:19:10</t>
+          <t>04-03-2026 17:41:44</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>05-03-2026 14:18:19</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4421,7 +4449,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26080522916810003879</t>
+          <t>26080522891580003816</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4445,12 +4473,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>348473</t>
+          <t>348177</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90638</t>
+          <t>90342</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4460,17 +4488,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO ADRIAN </t>
+          <t>FRANCISCO RUBEN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYALA </t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4480,7 +4508,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6462123059</t>
+          <t>6462588234</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4491,17 +4519,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23-10-1992</t>
+          <t>31-05-1988</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PEDROADRIAN523@GMAIL.COM</t>
+          <t>RUBENCONTRERAS767@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>04-03-2026 16:08:10</t>
+          <t>03-03-2026 17:28:07</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4526,12 +4554,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>04-03-2026 16:10:23</t>
+          <t>03-03-2026 17:29:17</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4548,7 +4576,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26080522886650003800</t>
+          <t>26080522850990003711</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4572,12 +4600,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>348599</t>
+          <t>348285</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90764</t>
+          <t>90450</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4587,17 +4615,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BRYAN FABRICIO</t>
+          <t>MAYA DANIELA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ECHEVERRIA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ALEGRE</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4607,47 +4635,43 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6863919612</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>6461922332</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-12-2003</t>
+          <t>03-12-2006</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BRYANRUIZ65@GMAIL.COM</t>
+          <t>MAYAMORENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>04-03-2026 20:20:01</t>
+          <t>03-03-2026 20:38:11</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4657,29 +4681,21 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>04-03-2026 20:26:28</t>
+          <t>03-03-2026 20:39:10</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>04-03-2026 20:25:57</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4687,7 +4703,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26080522899540003843</t>
+          <t>26080522861280003745</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4703,6 +4719,5663 @@
         </is>
       </c>
       <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>348473</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90638</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEDRO ADRIAN </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AYALA </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6462123059</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>23-10-1992</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>PEDROADRIAN523@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:08:10</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:10:23</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26080522886650003800</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>348698</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90863</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERICKA NAYELY </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GALVAN </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6461018907</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>12-10-1997</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>RAMIREZGALVAN12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:11:34</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:19:10</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:18:19</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26080522916810003879</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>348599</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90764</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BRYAN FABRICIO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ALEGRE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6863919612</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>21-12-2003</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>BRYANRUIZ65@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:20:01</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:26:28</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:25:57</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26080522899540003843</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>349004</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>91169</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>YARA DENISSE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6462723887</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>04-08-1998</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>YARADENISSEGOMEZALVAREZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:43:07</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:58:12</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26080523020090004129</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>NOEH CORDOVA ensenada</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>David Alejandro  Vasquez Felix</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>349550</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>91715</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MAGALI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6461854577</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>05-05-1987</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>MAGALIGONZALEZ67@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:30:43</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>10-03-2026 11:00:00</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:39:40</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26080523044460004187</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Israel  Buzo Zamora</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>349573</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91738</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MAGDALY</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ADAME</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6462708003</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>26-01-2000</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>MAGDALY76@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:54:59</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:01:07</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:00:09</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26080523020390004130</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>349356</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>91521</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ALMA YAMIN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BARRON</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6464001138</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>21-10-1993</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ALMA1993JIMENEZ8@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>09-03-2026 10:34:12</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>09-03-2026 10:35:33</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26080523003370004077</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>349548</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>91713</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALMA GISELA </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GAMEZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AGUILAR </t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6462135055</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>16-04-1973</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>GAMEZAGUILAR584@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:29:46</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:46:16</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:45:23</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26080523018980004124</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Israel  Buzo Zamora</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>349566</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>91731</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMAIRANY </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LEDESMA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6463258146</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10-02-1993</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>AMAYRANILEDESMA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:50:05</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:51:07</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26080523019430004125</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>348840</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>91005</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>JOSE ENRIQUE</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ANTUNA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FERREIRA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6462718690</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CALLE 11</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>28-09-1998</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>JEAFGD50@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>06-03-2026 07:30:26</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:36:32</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:36:05</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26080522997880004060</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>349480</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>91645</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ILIANA BERENICE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GAITAN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DOMINGUEZ </t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6462554792</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>17-04-1989</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>GAITANDDOMINGUEZ88@GAMIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:36:08</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:40:32</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:39:49</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26080523011960004096</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>349312</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>91477</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUGO </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMON </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6671880061</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>13-11-1976</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>HUGELEMON@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:59:29</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>11-03-2026 07:45:46</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>11-03-2026 07:45:04</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26080523082590004306</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>NOEH CORDOVA ensenada</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>349544</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>91709</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DAYRA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PEREZ </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7411188427</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>25-04-2007</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>DAYRADIAZ4564@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:23:20</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:24:37</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26080523017450004120</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>349565</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>91730</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DANNA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PIÑA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6465539722</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>20-01-1999</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>DANNAPIÑA65@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:48:53</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:55:32</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26080523019880004128</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>349568</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>91733</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MONIQUE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6465878596</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>09-08-1991</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>MONIQUEMUÑOZ76@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:50:58</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:51:46</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26080523019520004126</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>349635</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>91800</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DESTINY ADAHARA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6243558796</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>27-07-2006</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>DESTINYMDOMINGUEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:55:50</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>11-03-2026 16:57:46</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26080523094000004351</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>349639</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>91804</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARLA LEONOR </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALAZAR </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENDOZA </t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>5654908477</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>03-10-2007</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>MARLALEONOR12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:58:14</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>11-03-2026 16:59:17</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26080523094080004352</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>349154</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>91319</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARGARITA </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUZMAN </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALLEJO </t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6461141936</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>06-12-1980</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>MARGARITAGUZMA4@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:10:51</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:16:39</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:15:54</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26080522975620004027</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>350592</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>92756</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDGAR ROLANDO </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORTES </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESCALANTE </t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>7471402759</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>03-05-1994</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CORTESESCALANTE45@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>13-03-2026 15:01:42</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>13-03-2026 15:04:01</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26080523154270004490</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>349542</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>91707</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>KRISNA CAMILA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6611107604</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>21-05-2007</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CAMILAVALDEZ78@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:20:42</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:21:58</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26080523017240004119</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>349802</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>91967</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PATRICIA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BECERRIL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MURILLO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6462381358</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUNTA SAN GABRIEL </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>21-07-2000</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>PATRICIA.BECERRIL@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:23:39</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:30:06</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:29:24</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26080523048140004202</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>349838</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>92003</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>XAVIER</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>TERRIQUEZ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6641218753</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>02-01-1981</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>XTERRIQUEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:42:34</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:46:26</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26080523051740004220</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>350107</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>92272</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DIEGO GILBERTO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BASAÑEZ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7831150991</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>07-12-2007</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>DIEGOGUTIERREZ071214@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>11-03-2026 13:49:13</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>11-03-2026 13:50:53</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26080523089350004325</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>350691</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>92855</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>YESENIA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ESTEVA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6681959223</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>04-11-1999</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>PEREZESTEVA55@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>13-03-2026 20:20:03</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>13-03-2026 20:20:57</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26080523164450004524</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>350044</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>92209</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CHRISTIAN RENE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CARDONA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6461478737</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>28-08-2004</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CHRISTIANCARDONA1728@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>11-03-2026 08:04:29</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>11-03-2026 08:05:17</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26080523082910004308</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>350403</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>92567</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAOLA </t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SALGADO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PEREZ</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6461099220</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>13-06-1998</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>PAOLASALGADO5425@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>12-03-2026 17:35:08</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>12-03-2026 17:36:27</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26080523128810004435</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>350147</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>92312</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDRES </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CORTEZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6458463211</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>11-03-2000</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ASRFR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>11-03-2026 16:09:27</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>12-03-2026 13:49:35</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26080523122550004412</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>351553</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>93717</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CESAR OMAR </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MAYORAL</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ROLDAN </t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6461414664</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>16-09-2003</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>MAYORALROLDAN66@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:48:02</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:49:34</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26080523257140004665</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>351517</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>93681</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GISELA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOVELO </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6463414576</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>04-03-2006</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NOVELOSANTIAGO45@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:08:01</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:10:29</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26080523253830004654</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>351555</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>93719</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JULIO </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAYORAL </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ROLDAN</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6462361623</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>02-06-2011</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>JMAYORALR@EDUBC.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:52:45</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:54:13</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26080523257290004666</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>351599</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>93763</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>JESUS GUILLERMO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IRIBE </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>LAGUNA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6462721500</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>01-12-2007</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>LAGUNA66@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:38:54</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:40:01</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26080523262460004683</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>351222</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>93386</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ALEYDIS KARELY</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">URIAS </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>LUGO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6463832223</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>18-05-2003</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>URIASLUGO45@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>16-03-2026 15:18:59</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>16-03-2026 15:20:21</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26080523225150004596</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>350690</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>92854</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>KARLA DANIELA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUEVAS </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6462730128</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>15-03-2001</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>CUEVASGUTIERREZ55@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>13-03-2026 20:17:11</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>13-03-2026 20:18:18</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26080523164420004523</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>351191</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>93355</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>KARLA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>TELLEZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6461212141</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>02-12-2010</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>KARLATELLEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:53:16</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:12:45</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26080523251280004645</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>352037</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>94201</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EDGIN RAUL</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>GUERRERO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PORFIRIO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6463429271</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>24-09-2006</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>EDGINRAULGP@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>19-03-2026 07:26:18</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>19-03-2026 07:27:06</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26080523321520004830</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>351562</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>93726</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>IVANNA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SAMUDIO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AGUILAR</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6131048662</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>02-08-2003</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>SAMUDIOAGUILAR858@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:11:33</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:12:42</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26080523258030004670</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>351574</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>93738</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUNA </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>LLAMAS</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6463839019</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>15-09-2000</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>LUNALLAMAS55@GMAMIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:40:29</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:41:31</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26080523259320004674</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>351667</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>93831</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>JESUS MANUEL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6651180650</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>22-06-1996</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>MANUELRAMOSART@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:07:01</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:50:25</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:49:51</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26080523307770004804</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>NOEH CORDOVA ensenada</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>351668</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>93832</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ASTRID NICTE</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ROLLAND</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6461036549</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>12-07-1997</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>ASTRID.NICTE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:07:07</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:46:21</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:45:25</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26080523307560004802</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>NOEH CORDOVA ensenada</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Aaron Felipe Aguilar Grave</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>351981</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>94145</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>YURIDIA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOYA </t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6461217934</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>23-10-1988</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>YURIDIALOYA56@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:52:52</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:57:06</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:56:18</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26080523308190004807</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>351453</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>93617</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GILBERTO</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>FARIAS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6461894305</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>06-06-1999</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>GILBERTO9090@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>17-03-2026 10:30:14</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>17-03-2026 10:31:35</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26080523249540004638</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Christian Eduardo Hermosillo Diaz</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>351946</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>94110</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>INGRID KELESTHIA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>VILLALVA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RECINOS</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6466015531</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>11-03-1999</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>INGRIDRECINOSO66@GMIAL.COM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:33:59</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:39:09</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:38:13</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>26080523304000004791</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>352120</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>94284</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HANNIA </t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CISNEROS </t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6191200350</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>06-06-2006</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>LOPEZCISNEROS99@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>19-03-2026 15:38:42</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>19-03-2026 15:41:30</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>26080523331210004855</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
